--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
     </row>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
     </row>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C420"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,41 @@
           <t>状态</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>领取设备</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>开始时间</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>结束时间</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>重试次数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>下次可重试时间</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>失败原因</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -459,6 +494,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -474,6 +518,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -489,6 +542,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -504,6 +566,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -519,6 +590,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -534,6 +614,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -549,6 +638,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -564,6 +662,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -579,6 +686,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -594,6 +710,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -609,6 +734,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -624,6 +758,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -639,6 +782,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -654,6 +806,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -669,6 +830,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -684,6 +854,15 @@
           <t>已采集</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -699,6 +878,23 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:45:37</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nan；异常：name 'd' is not defined；异常：name 'd' is not defined；异常：name 'd' is not defined；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；单任务超时 240 秒；单任务超时 240 秒；单任务超时 240 秒；单任务超时 240 秒；单任务超时 240 秒；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -714,6 +910,35 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:49:41</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:53:41</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；单任务超时 240 秒</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:55:41</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -726,9 +951,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:37:54</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:38:55</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；规格不匹配；品名相似不足(ratio=35.7%)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -744,6 +994,35 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:13:55</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:17:55</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；单任务超时 240 秒</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:19:55</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -756,9 +1035,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:39:35</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:40:22</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -771,9 +1075,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:41:02</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:41:46</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -786,9 +1115,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:42:27</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:42:53</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -801,9 +1155,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:43:34</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:44:24</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -816,9 +1195,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:45:04</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:46:03</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -831,9 +1235,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:46:44</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:47:27</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -849,6 +1278,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -864,6 +1306,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -879,6 +1334,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -894,6 +1362,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -909,6 +1390,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -924,6 +1418,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -939,6 +1446,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -954,6 +1474,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -969,6 +1502,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -984,6 +1530,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -999,6 +1558,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1014,6 +1586,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1029,6 +1614,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1044,6 +1642,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1059,6 +1670,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1074,6 +1698,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1089,6 +1726,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1104,6 +1754,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1119,6 +1782,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1134,6 +1810,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1149,6 +1838,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1164,6 +1866,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1179,6 +1894,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1194,6 +1922,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1209,6 +1950,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1224,6 +1978,19 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1239,6 +2006,35 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:07:15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:11:15</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nan；单任务超时 240 秒</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:13:15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1254,6 +2050,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1269,6 +2074,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1284,6 +2098,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1299,6 +2122,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1314,6 +2146,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1329,6 +2170,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1344,6 +2194,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1359,6 +2218,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1374,6 +2242,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1389,6 +2266,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1404,6 +2290,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1419,6 +2314,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1434,6 +2338,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1449,6 +2362,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1464,6 +2386,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1479,6 +2410,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1494,6 +2434,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1509,6 +2458,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1524,6 +2482,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1539,6 +2506,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1554,6 +2530,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1569,6 +2554,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1584,6 +2578,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1599,6 +2602,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1614,6 +2626,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1629,6 +2650,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1644,6 +2674,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1659,6 +2698,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1674,6 +2722,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1689,6 +2746,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1704,6 +2770,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1719,6 +2794,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1734,6 +2818,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1749,6 +2842,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1764,6 +2866,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1779,6 +2890,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1794,6 +2914,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1809,6 +2938,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1824,6 +2962,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1839,6 +2986,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1854,6 +3010,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1869,6 +3034,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1884,6 +3058,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1899,6 +3082,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1914,6 +3106,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1929,6 +3130,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1944,6 +3154,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1959,6 +3178,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1974,6 +3202,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1989,6 +3226,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2004,6 +3250,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2019,6 +3274,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2034,6 +3298,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2049,6 +3322,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2064,6 +3346,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2079,6 +3370,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2094,6 +3394,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2109,6 +3418,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2124,6 +3442,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2139,6 +3466,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2154,6 +3490,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2169,6 +3514,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2184,6 +3538,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2199,6 +3562,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2214,6 +3586,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2229,6 +3610,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2244,6 +3634,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2259,6 +3658,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2274,6 +3682,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2289,6 +3706,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2304,6 +3730,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2319,6 +3754,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2334,6 +3778,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2349,6 +3802,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2364,6 +3826,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2379,6 +3850,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2394,6 +3874,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2409,6 +3898,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2424,6 +3922,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2439,6 +3946,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2454,6 +3970,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2469,6 +3994,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2484,6 +4018,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2499,6 +4042,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2514,6 +4066,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2529,6 +4090,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2544,6 +4114,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2559,6 +4138,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2574,6 +4162,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2589,6 +4186,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2604,6 +4210,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2619,6 +4234,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2634,6 +4258,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2649,6 +4282,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2664,6 +4306,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2679,6 +4330,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2694,6 +4354,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2709,6 +4378,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2724,6 +4402,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2739,6 +4426,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2754,6 +4450,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2769,6 +4474,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2784,6 +4498,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2799,6 +4522,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2814,6 +4546,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2829,6 +4570,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2844,6 +4594,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2859,6 +4618,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2874,6 +4642,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2889,6 +4666,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2904,6 +4690,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2919,6 +4714,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2934,6 +4738,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2949,6 +4762,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2964,6 +4786,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2979,6 +4810,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2994,6 +4834,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3009,6 +4858,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3024,6 +4882,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3039,6 +4906,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3054,6 +4930,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3069,6 +4954,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3084,6 +4978,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3099,6 +5002,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3114,6 +5026,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3129,6 +5050,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3144,6 +5074,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3159,6 +5098,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3174,6 +5122,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3189,6 +5146,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3204,6 +5170,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3219,6 +5194,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3234,6 +5218,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3249,6 +5242,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3264,6 +5266,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3279,6 +5290,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3294,6 +5314,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3309,6 +5338,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3324,6 +5362,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3339,6 +5386,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3354,6 +5410,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3369,6 +5434,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3384,6 +5458,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3399,6 +5482,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3414,6 +5506,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3429,6 +5530,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3444,6 +5554,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3459,6 +5578,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3474,6 +5602,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3489,6 +5626,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3504,6 +5650,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3519,6 +5674,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3534,6 +5698,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3549,6 +5722,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3564,6 +5746,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3579,6 +5770,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3594,6 +5794,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3609,6 +5818,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3624,6 +5842,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3639,6 +5866,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3654,6 +5890,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3669,6 +5914,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3684,6 +5938,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3699,6 +5962,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3714,6 +5986,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3729,6 +6010,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3744,6 +6034,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3759,6 +6058,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3774,6 +6082,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -3789,6 +6106,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -3804,6 +6130,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -3819,6 +6154,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -3834,6 +6178,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -3849,6 +6202,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -3864,6 +6226,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -3879,6 +6250,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -3894,6 +6274,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -3909,6 +6298,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -3924,6 +6322,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3939,6 +6346,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3954,6 +6370,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -3969,6 +6394,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -3984,6 +6418,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -3999,6 +6442,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4014,6 +6466,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4029,6 +6490,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4044,6 +6514,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4059,6 +6538,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4074,6 +6562,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4089,6 +6586,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4104,6 +6610,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4119,6 +6634,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4134,6 +6658,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4149,6 +6682,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4164,6 +6706,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4179,6 +6730,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4194,6 +6754,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4209,6 +6778,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4224,6 +6802,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4239,6 +6826,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4254,6 +6850,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4269,6 +6874,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4284,6 +6898,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4299,6 +6922,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4314,6 +6946,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4329,6 +6970,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4344,6 +6994,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4359,6 +7018,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4374,6 +7042,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4389,6 +7066,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4404,6 +7090,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4419,6 +7114,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4434,6 +7138,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4449,6 +7162,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4464,6 +7186,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4479,6 +7210,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4494,6 +7234,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4509,6 +7258,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4524,6 +7282,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4539,6 +7306,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4554,6 +7330,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4569,6 +7354,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4584,6 +7378,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4599,6 +7402,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4614,6 +7426,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4629,6 +7450,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4644,6 +7474,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4659,6 +7498,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4674,6 +7522,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4689,6 +7546,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4704,6 +7570,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4719,6 +7594,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -4734,6 +7618,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -4749,6 +7642,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -4764,6 +7666,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -4779,6 +7690,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -4794,6 +7714,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -4809,6 +7738,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -4824,6 +7762,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -4839,6 +7786,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -4854,6 +7810,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -4869,6 +7834,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -4884,6 +7858,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -4899,6 +7882,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -4914,6 +7906,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -4929,6 +7930,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -4944,6 +7954,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -4959,6 +7978,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -4974,6 +8002,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -4989,6 +8026,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5004,6 +8050,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5019,6 +8074,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5034,6 +8098,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5049,6 +8122,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5064,6 +8146,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5079,6 +8170,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5094,6 +8194,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5109,6 +8218,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="n">
+        <v>0</v>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5124,6 +8242,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5139,6 +8266,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5154,6 +8290,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5169,6 +8314,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5184,6 +8338,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5199,6 +8362,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5214,6 +8386,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5229,6 +8410,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5244,6 +8434,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5259,6 +8458,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5274,6 +8482,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5289,6 +8506,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5304,6 +8530,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="n">
+        <v>0</v>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5319,6 +8554,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5334,6 +8578,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5349,6 +8602,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5364,6 +8626,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="n">
+        <v>0</v>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5379,6 +8650,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5394,6 +8674,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5409,6 +8698,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5424,6 +8722,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5439,6 +8746,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5454,6 +8770,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5469,6 +8794,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5484,6 +8818,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5499,6 +8842,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5514,6 +8866,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5529,6 +8890,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5544,6 +8914,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5559,6 +8938,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5574,6 +8962,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5589,6 +8986,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5604,6 +9010,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="n">
+        <v>0</v>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -5619,6 +9034,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -5634,6 +9058,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -5649,6 +9082,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -5664,6 +9106,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -5679,6 +9130,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -5694,6 +9154,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="n">
+        <v>0</v>
+      </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -5709,6 +9178,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="n">
+        <v>0</v>
+      </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -5724,6 +9202,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -5739,6 +9226,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -5754,6 +9250,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -5769,6 +9274,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -5784,6 +9298,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -5799,6 +9322,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -5814,6 +9346,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -5829,6 +9370,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="n">
+        <v>0</v>
+      </c>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -5844,6 +9394,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -5859,6 +9418,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -5874,6 +9442,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -5889,6 +9466,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -5904,6 +9490,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -5919,6 +9514,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -5934,6 +9538,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -5949,6 +9562,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -5964,6 +9586,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -5979,6 +9610,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="n">
+        <v>0</v>
+      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -5994,6 +9634,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -6009,6 +9658,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -6024,6 +9682,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -6039,6 +9706,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="n">
+        <v>0</v>
+      </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -6054,6 +9730,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -6069,6 +9754,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -6084,6 +9778,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -6099,6 +9802,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -6114,6 +9826,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -6129,6 +9850,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -6144,6 +9874,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -6159,6 +9898,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -6174,6 +9922,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -6189,6 +9946,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -6204,6 +9970,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -6219,6 +9994,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -6234,6 +10018,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -6249,6 +10042,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -6264,6 +10066,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -6279,6 +10090,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="n">
+        <v>0</v>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -6294,6 +10114,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -6309,6 +10138,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -6324,6 +10162,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -6339,6 +10186,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -6354,6 +10210,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -6369,6 +10234,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -6384,6 +10258,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -6399,6 +10282,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -6414,6 +10306,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -6429,6 +10330,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -6444,6 +10354,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="n">
+        <v>0</v>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -6459,6 +10378,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="n">
+        <v>0</v>
+      </c>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -6474,6 +10402,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -6489,6 +10426,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -6504,6 +10450,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="n">
+        <v>0</v>
+      </c>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -6519,6 +10474,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -6534,6 +10498,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -6549,6 +10522,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -6564,6 +10546,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -6579,6 +10570,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="n">
+        <v>0</v>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -6594,6 +10594,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="n">
+        <v>0</v>
+      </c>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -6609,6 +10618,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -6624,6 +10642,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="n">
+        <v>0</v>
+      </c>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -6639,6 +10666,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -6654,6 +10690,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>0</v>
+      </c>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -6669,6 +10714,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -6684,6 +10738,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -6699,6 +10762,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -6714,6 +10786,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -6729,6 +10810,15 @@
           <t>未采集</t>
         </is>
       </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -1275,12 +1275,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:21:10</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:21:51</t>
+        </is>
+      </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
@@ -1303,12 +1315,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:22:32</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:23:08</t>
+        </is>
+      </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
@@ -1331,12 +1355,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:23:48</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:24:40</t>
+        </is>
+      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
@@ -1359,12 +1395,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:25:20</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-09 12:26:09</t>
+        </is>
+      </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
@@ -1387,18 +1435,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:06:20</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:07:38</t>
+        </is>
+      </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；规格不匹配</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1415,18 +1475,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:08:18</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:09:35</t>
+        </is>
+      </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；规格不匹配</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -494,9 +494,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:31:15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:32:07</t>
+        </is>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -518,9 +530,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:32:47</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:34:09</t>
+        </is>
+      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
@@ -542,9 +566,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:08:05</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:09:07</t>
+        </is>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -566,9 +602,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:09:47</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:10:43</t>
+        </is>
+      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
@@ -590,9 +638,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:11:23</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:12:25</t>
+        </is>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -614,9 +674,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:13:20</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:14:14</t>
+        </is>
+      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
@@ -638,9 +710,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:14:55</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:15:35</t>
+        </is>
+      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -659,16 +743,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:16:15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:17:09</t>
+        </is>
+      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
     </row>
@@ -683,16 +783,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:17:49</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:19:01</t>
+        </is>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=40.0%)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
     </row>
@@ -710,9 +826,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:19:41</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:20:07</t>
+        </is>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -734,9 +862,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:20:47</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:21:18</t>
+        </is>
+      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
@@ -758,9 +898,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:21:58</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:22:51</t>
+        </is>
+      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
@@ -782,9 +934,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:23:31</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:24:18</t>
+        </is>
+      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
@@ -806,9 +970,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:24:58</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:25:25</t>
+        </is>
+      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
@@ -830,9 +1006,21 @@
           <t>已采集</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:26:05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:26:54</t>
+        </is>
+      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
@@ -851,16 +1039,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:28:55</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:29:48</t>
+        </is>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=27.3%)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
     </row>
@@ -875,22 +1079,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:30:28</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-08 16:45:37</t>
+          <t>2026-05-09 17:31:18</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>nan；异常：name 'd' is not defined；异常：name 'd' is not defined；异常：name 'd' is not defined；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；单任务超时 240 秒；单任务超时 240 秒；单任务超时 240 秒；单任务超时 240 秒；单任务超时 240 秒；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
+          <t>nan；品名相似不足(ratio=10.0%)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -907,7 +1119,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -917,27 +1129,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-08 16:49:41</t>
+          <t>2026-05-09 17:31:58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-08 16:53:41</t>
+          <t>2026-05-09 17:32:53</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；单任务超时 240 秒</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-08 16:55:41</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -961,12 +1165,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-09 11:37:54</t>
+          <t>2026-05-09 17:33:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-09 11:38:55</t>
+          <t>2026-05-09 17:34:28</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -974,7 +1178,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；规格不匹配；品名相似不足(ratio=35.7%)</t>
+          <t>nan；规格不匹配；品名相似不足(ratio=35.7%)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -991,7 +1195,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1001,27 +1205,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-08 17:13:55</t>
+          <t>2026-05-09 17:35:08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-08 17:17:55</t>
+          <t>2026-05-09 17:36:00</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；单任务超时 240 秒</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-08 17:19:55</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1045,22 +1241,18 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-09 11:39:35</t>
+          <t>2026-05-09 17:36:40</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-09 11:40:22</t>
+          <t>2026-05-09 17:37:29</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
     </row>
@@ -1085,22 +1277,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-09 11:41:02</t>
+          <t>2026-05-09 17:38:09</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-09 11:41:46</t>
+          <t>2026-05-09 17:38:41</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
     </row>
@@ -1115,32 +1303,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:42:27</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:42:53</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
     </row>
@@ -1155,32 +1325,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:43:34</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:44:24</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
     </row>
@@ -1195,32 +1347,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:45:04</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:46:03</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
     </row>
@@ -1235,32 +1369,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:46:44</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:47:27</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
     </row>
@@ -1275,32 +1391,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:21:10</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:21:51</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
     </row>
@@ -1315,32 +1413,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:22:32</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:23:08</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
     </row>
@@ -1355,32 +1435,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:23:48</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:24:40</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
     </row>
@@ -1395,32 +1457,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:25:20</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-09 12:26:09</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
     </row>
@@ -1435,32 +1479,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-05-09 14:06:20</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-09 14:07:38</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；规格不匹配</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
     </row>
@@ -1475,32 +1501,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-05-09 14:08:18</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-09 14:09:35</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）；规格不匹配</t>
-        </is>
-      </c>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
     </row>
@@ -1521,14 +1529,8 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
     </row>
@@ -1549,14 +1551,8 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
     </row>
@@ -1577,14 +1573,8 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
     </row>
@@ -1605,14 +1595,8 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -1633,14 +1617,8 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -1661,14 +1639,8 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
     </row>
@@ -1689,14 +1661,8 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
     </row>
@@ -1717,14 +1683,8 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
     </row>
@@ -1745,14 +1705,8 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
     </row>
@@ -1773,14 +1727,8 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
     </row>
@@ -1801,14 +1749,8 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
     </row>
@@ -1829,14 +1771,8 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
     </row>
@@ -1857,14 +1793,8 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
     </row>
@@ -1885,14 +1815,8 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
     </row>
@@ -1913,14 +1837,8 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
     </row>
@@ -1941,14 +1859,8 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
     </row>
@@ -1969,14 +1881,8 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
     </row>
@@ -1997,14 +1903,8 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -2025,14 +1925,8 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
     </row>
@@ -2053,14 +1947,8 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>nan；采集中超时回收（原设备 3B6F6AE7SX2MCMB9）</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
     </row>
@@ -2078,34 +1966,12 @@
           <t>未采集</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>3B6F6AE7SX2MCMB9</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-05-08 17:07:15</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-08 17:11:15</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>nan；单任务超时 240 秒</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-05-08 17:13:15</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2125,9 +1991,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -2149,9 +2013,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -2173,9 +2035,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -2197,9 +2057,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -2221,9 +2079,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -2245,9 +2101,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -2269,9 +2123,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -2293,9 +2145,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -2317,9 +2167,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -2341,9 +2189,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -2365,9 +2211,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -2389,9 +2233,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -2413,9 +2255,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -2437,9 +2277,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -2461,9 +2299,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -2485,9 +2321,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -2509,9 +2343,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -2533,9 +2365,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -2557,9 +2387,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -2581,9 +2409,7 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -2605,9 +2431,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -2629,9 +2453,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -2653,9 +2475,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
@@ -2677,9 +2497,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -2701,9 +2519,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -2725,9 +2541,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -2749,9 +2563,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
@@ -2773,9 +2585,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
@@ -2797,9 +2607,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
@@ -2821,9 +2629,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
@@ -2845,9 +2651,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
@@ -2869,9 +2673,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -2893,9 +2695,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
@@ -2917,9 +2717,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -2941,9 +2739,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -2965,9 +2761,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
@@ -2989,9 +2783,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
@@ -3013,9 +2805,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
@@ -3037,9 +2827,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -3061,9 +2849,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
@@ -3085,9 +2871,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
@@ -3109,9 +2893,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
@@ -3133,9 +2915,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -3157,9 +2937,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -3181,9 +2959,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -3205,9 +2981,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
@@ -3229,9 +3003,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
@@ -3253,9 +3025,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -3277,9 +3047,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -3301,9 +3069,7 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -3325,9 +3091,7 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -3349,9 +3113,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
@@ -3373,9 +3135,7 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -3397,9 +3157,7 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -3421,9 +3179,7 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -3445,9 +3201,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -3469,9 +3223,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
@@ -3493,9 +3245,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
@@ -3517,9 +3267,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
@@ -3541,9 +3289,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
@@ -3565,9 +3311,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
@@ -3589,9 +3333,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
@@ -3613,9 +3355,7 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
@@ -3637,9 +3377,7 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
@@ -3661,9 +3399,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -3685,9 +3421,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
@@ -3709,9 +3443,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
@@ -3733,9 +3465,7 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
@@ -3757,9 +3487,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
@@ -3781,9 +3509,7 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
@@ -3805,9 +3531,7 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
@@ -3829,9 +3553,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
@@ -3853,9 +3575,7 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
@@ -3877,9 +3597,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
@@ -3901,9 +3619,7 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
@@ -3925,9 +3641,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
@@ -3949,9 +3663,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
@@ -3973,9 +3685,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
@@ -3997,9 +3707,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
@@ -4021,9 +3729,7 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
@@ -4045,9 +3751,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
@@ -4069,9 +3773,7 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
@@ -4093,9 +3795,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
@@ -4117,9 +3817,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
@@ -4141,9 +3839,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
@@ -4165,9 +3861,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
@@ -4189,9 +3883,7 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
@@ -4213,9 +3905,7 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
@@ -4237,9 +3927,7 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
@@ -4261,9 +3949,7 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
@@ -4285,9 +3971,7 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="n">
-        <v>0</v>
-      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
@@ -4309,9 +3993,7 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="n">
-        <v>0</v>
-      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
@@ -4333,9 +4015,7 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
@@ -4357,9 +4037,7 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
@@ -4381,9 +4059,7 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="n">
-        <v>0</v>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
@@ -4405,9 +4081,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="n">
-        <v>0</v>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
@@ -4429,9 +4103,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="n">
-        <v>0</v>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
@@ -4453,9 +4125,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>0</v>
-      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
@@ -4477,9 +4147,7 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
@@ -4501,9 +4169,7 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
@@ -4525,9 +4191,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
@@ -4549,9 +4213,7 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
@@ -4573,9 +4235,7 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="n">
-        <v>0</v>
-      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
@@ -4597,9 +4257,7 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
@@ -4621,9 +4279,7 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
@@ -4645,9 +4301,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
@@ -4669,9 +4323,7 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
@@ -4693,9 +4345,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
@@ -4717,9 +4367,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
@@ -4741,9 +4389,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
@@ -4765,9 +4411,7 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
@@ -4789,9 +4433,7 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
@@ -4813,9 +4455,7 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
@@ -4837,9 +4477,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="n">
-        <v>0</v>
-      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
@@ -4861,9 +4499,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="n">
-        <v>0</v>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
@@ -4885,9 +4521,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="n">
-        <v>0</v>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
@@ -4909,9 +4543,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="n">
-        <v>0</v>
-      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
@@ -4933,9 +4565,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="n">
-        <v>0</v>
-      </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
@@ -4957,9 +4587,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="n">
-        <v>0</v>
-      </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
@@ -4981,9 +4609,7 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
@@ -5005,9 +4631,7 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="n">
-        <v>0</v>
-      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
@@ -5029,9 +4653,7 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
@@ -5053,9 +4675,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
@@ -5077,9 +4697,7 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="n">
-        <v>0</v>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
@@ -5101,9 +4719,7 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
@@ -5125,9 +4741,7 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="n">
-        <v>0</v>
-      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
@@ -5149,9 +4763,7 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
@@ -5173,9 +4785,7 @@
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
@@ -5197,9 +4807,7 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="n">
-        <v>0</v>
-      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
@@ -5221,9 +4829,7 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
@@ -5245,9 +4851,7 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
@@ -5269,9 +4873,7 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="n">
-        <v>0</v>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
@@ -5293,9 +4895,7 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
@@ -5317,9 +4917,7 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="n">
-        <v>0</v>
-      </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
@@ -5341,9 +4939,7 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="n">
-        <v>0</v>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
@@ -5365,9 +4961,7 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="n">
-        <v>0</v>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
@@ -5389,9 +4983,7 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="n">
-        <v>0</v>
-      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
@@ -5413,9 +5005,7 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="n">
-        <v>0</v>
-      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
@@ -5437,9 +5027,7 @@
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
@@ -5461,9 +5049,7 @@
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
@@ -5485,9 +5071,7 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
@@ -5509,9 +5093,7 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
@@ -5533,9 +5115,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
@@ -5557,9 +5137,7 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="n">
-        <v>0</v>
-      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
@@ -5581,9 +5159,7 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
@@ -5605,9 +5181,7 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
@@ -5629,9 +5203,7 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="n">
-        <v>0</v>
-      </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
@@ -5653,9 +5225,7 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
@@ -5677,9 +5247,7 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="n">
-        <v>0</v>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
@@ -5701,9 +5269,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="n">
-        <v>0</v>
-      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
@@ -5725,9 +5291,7 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
@@ -5749,9 +5313,7 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
-      <c r="G206" t="n">
-        <v>0</v>
-      </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
@@ -5773,9 +5335,7 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
@@ -5797,9 +5357,7 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
@@ -5821,9 +5379,7 @@
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
@@ -5845,9 +5401,7 @@
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
@@ -5869,9 +5423,7 @@
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" t="n">
-        <v>0</v>
-      </c>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
@@ -5893,9 +5445,7 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
@@ -5917,9 +5467,7 @@
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
@@ -5941,9 +5489,7 @@
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
@@ -5965,9 +5511,7 @@
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
@@ -5989,9 +5533,7 @@
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
-      <c r="G216" t="n">
-        <v>0</v>
-      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
@@ -6013,9 +5555,7 @@
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" t="n">
-        <v>0</v>
-      </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
@@ -6037,9 +5577,7 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="n">
-        <v>0</v>
-      </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
@@ -6061,9 +5599,7 @@
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
@@ -6085,9 +5621,7 @@
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
@@ -6109,9 +5643,7 @@
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
@@ -6133,9 +5665,7 @@
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" t="n">
-        <v>0</v>
-      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
@@ -6157,9 +5687,7 @@
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
-      <c r="G223" t="n">
-        <v>0</v>
-      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
@@ -6181,9 +5709,7 @@
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" t="n">
-        <v>0</v>
-      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
@@ -6205,9 +5731,7 @@
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
@@ -6229,9 +5753,7 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="n">
-        <v>0</v>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
@@ -6253,9 +5775,7 @@
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
@@ -6277,9 +5797,7 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" t="n">
-        <v>0</v>
-      </c>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
@@ -6301,9 +5819,7 @@
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
-      <c r="G229" t="n">
-        <v>0</v>
-      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
@@ -6325,9 +5841,7 @@
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
@@ -6349,9 +5863,7 @@
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
@@ -6373,9 +5885,7 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
-      <c r="G232" t="n">
-        <v>0</v>
-      </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
@@ -6397,9 +5907,7 @@
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
-      <c r="G233" t="n">
-        <v>0</v>
-      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
@@ -6421,9 +5929,7 @@
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
-      <c r="G234" t="n">
-        <v>0</v>
-      </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
@@ -6445,9 +5951,7 @@
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
@@ -6469,9 +5973,7 @@
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
-      <c r="G236" t="n">
-        <v>0</v>
-      </c>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
@@ -6493,9 +5995,7 @@
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="n">
-        <v>0</v>
-      </c>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
@@ -6517,9 +6017,7 @@
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" t="n">
-        <v>0</v>
-      </c>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
@@ -6541,9 +6039,7 @@
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
@@ -6565,9 +6061,7 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="n">
-        <v>0</v>
-      </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
@@ -6589,9 +6083,7 @@
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" t="n">
-        <v>0</v>
-      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
@@ -6613,9 +6105,7 @@
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
-      <c r="G242" t="n">
-        <v>0</v>
-      </c>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
@@ -6637,9 +6127,7 @@
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
@@ -6661,9 +6149,7 @@
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
-      <c r="G244" t="n">
-        <v>0</v>
-      </c>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
@@ -6685,9 +6171,7 @@
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr"/>
-      <c r="G245" t="n">
-        <v>0</v>
-      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
@@ -6709,9 +6193,7 @@
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr"/>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
@@ -6733,9 +6215,7 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
-      <c r="G247" t="n">
-        <v>0</v>
-      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
@@ -6757,9 +6237,7 @@
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
-      <c r="G248" t="n">
-        <v>0</v>
-      </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
@@ -6781,9 +6259,7 @@
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="n">
-        <v>0</v>
-      </c>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
@@ -6805,9 +6281,7 @@
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
@@ -6829,9 +6303,7 @@
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
-      <c r="G251" t="n">
-        <v>0</v>
-      </c>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
@@ -6853,9 +6325,7 @@
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
@@ -6877,9 +6347,7 @@
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
@@ -6901,9 +6369,7 @@
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
@@ -6925,9 +6391,7 @@
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
@@ -6949,9 +6413,7 @@
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
+      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
@@ -6973,9 +6435,7 @@
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
@@ -6997,9 +6457,7 @@
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
@@ -7021,9 +6479,7 @@
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="n">
-        <v>0</v>
-      </c>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
@@ -7045,9 +6501,7 @@
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="n">
-        <v>0</v>
-      </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
@@ -7069,9 +6523,7 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr"/>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
@@ -7093,9 +6545,7 @@
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr"/>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
@@ -7117,9 +6567,7 @@
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr"/>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
@@ -7141,9 +6589,7 @@
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr"/>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
@@ -7165,9 +6611,7 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
@@ -7189,9 +6633,7 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" t="n">
-        <v>0</v>
-      </c>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
@@ -7213,9 +6655,7 @@
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr"/>
-      <c r="G267" t="n">
-        <v>0</v>
-      </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
@@ -7237,9 +6677,7 @@
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr"/>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
@@ -7261,9 +6699,7 @@
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="n">
-        <v>0</v>
-      </c>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
@@ -7285,9 +6721,7 @@
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
-      <c r="G270" t="n">
-        <v>0</v>
-      </c>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
@@ -7309,9 +6743,7 @@
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
@@ -7333,9 +6765,7 @@
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" t="n">
-        <v>0</v>
-      </c>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
@@ -7357,9 +6787,7 @@
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr"/>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
@@ -7381,9 +6809,7 @@
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="n">
-        <v>0</v>
-      </c>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
@@ -7405,9 +6831,7 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
@@ -7429,9 +6853,7 @@
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
-      <c r="G276" t="n">
-        <v>0</v>
-      </c>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
@@ -7453,9 +6875,7 @@
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
@@ -7477,9 +6897,7 @@
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
@@ -7501,9 +6919,7 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
@@ -7525,9 +6941,7 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
@@ -7549,9 +6963,7 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr"/>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
@@ -7573,9 +6985,7 @@
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="n">
-        <v>0</v>
-      </c>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
@@ -7597,9 +7007,7 @@
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr"/>
-      <c r="G283" t="n">
-        <v>0</v>
-      </c>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
@@ -7621,9 +7029,7 @@
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
@@ -7645,9 +7051,7 @@
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr"/>
-      <c r="G285" t="n">
-        <v>0</v>
-      </c>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
@@ -7669,9 +7073,7 @@
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" t="n">
-        <v>0</v>
-      </c>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
@@ -7693,9 +7095,7 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" t="n">
-        <v>0</v>
-      </c>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
@@ -7717,9 +7117,7 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr"/>
-      <c r="G288" t="n">
-        <v>0</v>
-      </c>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
@@ -7741,9 +7139,7 @@
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr"/>
-      <c r="G289" t="n">
-        <v>0</v>
-      </c>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
@@ -7765,9 +7161,7 @@
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
@@ -7789,9 +7183,7 @@
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
-      <c r="G291" t="n">
-        <v>0</v>
-      </c>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
@@ -7813,9 +7205,7 @@
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
-      <c r="G292" t="n">
-        <v>0</v>
-      </c>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
@@ -7837,9 +7227,7 @@
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
-      <c r="G293" t="n">
-        <v>0</v>
-      </c>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
@@ -7861,9 +7249,7 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
-      <c r="G294" t="n">
-        <v>0</v>
-      </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
@@ -7885,9 +7271,7 @@
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr"/>
-      <c r="G295" t="n">
-        <v>0</v>
-      </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
@@ -7909,9 +7293,7 @@
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr"/>
-      <c r="G296" t="n">
-        <v>0</v>
-      </c>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
@@ -7933,9 +7315,7 @@
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="n">
-        <v>0</v>
-      </c>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr"/>
@@ -7957,9 +7337,7 @@
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
@@ -7981,9 +7359,7 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
-      <c r="G299" t="n">
-        <v>0</v>
-      </c>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
@@ -8005,9 +7381,7 @@
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
-      <c r="G300" t="n">
-        <v>0</v>
-      </c>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
@@ -8029,9 +7403,7 @@
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
-      <c r="G301" t="n">
-        <v>0</v>
-      </c>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
@@ -8053,9 +7425,7 @@
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
@@ -8077,9 +7447,7 @@
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
-      <c r="G303" t="n">
-        <v>0</v>
-      </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
@@ -8101,9 +7469,7 @@
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="n">
-        <v>0</v>
-      </c>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
@@ -8125,9 +7491,7 @@
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
-      <c r="G305" t="n">
-        <v>0</v>
-      </c>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
@@ -8149,9 +7513,7 @@
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
-      <c r="G306" t="n">
-        <v>0</v>
-      </c>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
@@ -8173,9 +7535,7 @@
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr"/>
-      <c r="G307" t="n">
-        <v>0</v>
-      </c>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
@@ -8197,9 +7557,7 @@
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr"/>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
@@ -8221,9 +7579,7 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr"/>
-      <c r="G309" t="n">
-        <v>0</v>
-      </c>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
@@ -8245,9 +7601,7 @@
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr"/>
-      <c r="G310" t="n">
-        <v>0</v>
-      </c>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
@@ -8269,9 +7623,7 @@
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr"/>
-      <c r="G311" t="n">
-        <v>0</v>
-      </c>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
@@ -8293,9 +7645,7 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr"/>
-      <c r="G312" t="n">
-        <v>0</v>
-      </c>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
@@ -8317,9 +7667,7 @@
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr"/>
-      <c r="G313" t="n">
-        <v>0</v>
-      </c>
+      <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
@@ -8341,9 +7689,7 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr"/>
-      <c r="G314" t="n">
-        <v>0</v>
-      </c>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
@@ -8365,9 +7711,7 @@
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr"/>
-      <c r="G315" t="n">
-        <v>0</v>
-      </c>
+      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
@@ -8389,9 +7733,7 @@
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr"/>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
+      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
@@ -8413,9 +7755,7 @@
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr"/>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
+      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
@@ -8437,9 +7777,7 @@
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr"/>
-      <c r="G318" t="n">
-        <v>0</v>
-      </c>
+      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr"/>
@@ -8461,9 +7799,7 @@
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr"/>
-      <c r="G319" t="n">
-        <v>0</v>
-      </c>
+      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
@@ -8485,9 +7821,7 @@
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr"/>
-      <c r="G320" t="n">
-        <v>0</v>
-      </c>
+      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
@@ -8509,9 +7843,7 @@
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr"/>
-      <c r="G321" t="n">
-        <v>0</v>
-      </c>
+      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
@@ -8533,9 +7865,7 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr"/>
-      <c r="G322" t="n">
-        <v>0</v>
-      </c>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
@@ -8557,9 +7887,7 @@
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr"/>
-      <c r="G323" t="n">
-        <v>0</v>
-      </c>
+      <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
@@ -8581,9 +7909,7 @@
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr"/>
-      <c r="G324" t="n">
-        <v>0</v>
-      </c>
+      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
@@ -8605,9 +7931,7 @@
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr"/>
-      <c r="G325" t="n">
-        <v>0</v>
-      </c>
+      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
@@ -8629,9 +7953,7 @@
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr"/>
-      <c r="G326" t="n">
-        <v>0</v>
-      </c>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
@@ -8653,9 +7975,7 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr"/>
-      <c r="G327" t="n">
-        <v>0</v>
-      </c>
+      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
@@ -8677,9 +7997,7 @@
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr"/>
-      <c r="G328" t="n">
-        <v>0</v>
-      </c>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr"/>
@@ -8701,9 +8019,7 @@
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr"/>
-      <c r="G329" t="n">
-        <v>0</v>
-      </c>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
@@ -8725,9 +8041,7 @@
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr"/>
-      <c r="G330" t="n">
-        <v>0</v>
-      </c>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
@@ -8749,9 +8063,7 @@
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr"/>
-      <c r="G331" t="n">
-        <v>0</v>
-      </c>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
@@ -8773,9 +8085,7 @@
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr"/>
-      <c r="G332" t="n">
-        <v>0</v>
-      </c>
+      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
@@ -8797,9 +8107,7 @@
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr"/>
-      <c r="G333" t="n">
-        <v>0</v>
-      </c>
+      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
@@ -8821,9 +8129,7 @@
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr"/>
-      <c r="G334" t="n">
-        <v>0</v>
-      </c>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
@@ -8845,9 +8151,7 @@
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr"/>
-      <c r="G335" t="n">
-        <v>0</v>
-      </c>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
@@ -8869,9 +8173,7 @@
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr"/>
-      <c r="G336" t="n">
-        <v>0</v>
-      </c>
+      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
@@ -8893,9 +8195,7 @@
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr"/>
-      <c r="G337" t="n">
-        <v>0</v>
-      </c>
+      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
@@ -8917,9 +8217,7 @@
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
-      <c r="G338" t="n">
-        <v>0</v>
-      </c>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
@@ -8941,9 +8239,7 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
-      <c r="G339" t="n">
-        <v>0</v>
-      </c>
+      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
@@ -8965,9 +8261,7 @@
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr"/>
-      <c r="G340" t="n">
-        <v>0</v>
-      </c>
+      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
@@ -8989,9 +8283,7 @@
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr"/>
-      <c r="G341" t="n">
-        <v>0</v>
-      </c>
+      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
@@ -9013,9 +8305,7 @@
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr"/>
-      <c r="G342" t="n">
-        <v>0</v>
-      </c>
+      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr"/>
@@ -9037,9 +8327,7 @@
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr"/>
-      <c r="G343" t="n">
-        <v>0</v>
-      </c>
+      <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
@@ -9061,9 +8349,7 @@
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
-      <c r="G344" t="n">
-        <v>0</v>
-      </c>
+      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
@@ -9085,9 +8371,7 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
-      <c r="G345" t="n">
-        <v>0</v>
-      </c>
+      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
@@ -9109,9 +8393,7 @@
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr"/>
-      <c r="G346" t="n">
-        <v>0</v>
-      </c>
+      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
@@ -9133,9 +8415,7 @@
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr"/>
-      <c r="G347" t="n">
-        <v>0</v>
-      </c>
+      <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
@@ -9157,9 +8437,7 @@
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr"/>
-      <c r="G348" t="n">
-        <v>0</v>
-      </c>
+      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
@@ -9181,9 +8459,7 @@
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr"/>
-      <c r="G349" t="n">
-        <v>0</v>
-      </c>
+      <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
@@ -9205,9 +8481,7 @@
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr"/>
-      <c r="G350" t="n">
-        <v>0</v>
-      </c>
+      <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
@@ -9229,9 +8503,7 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr"/>
-      <c r="G351" t="n">
-        <v>0</v>
-      </c>
+      <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
@@ -9253,9 +8525,7 @@
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr"/>
-      <c r="G352" t="n">
-        <v>0</v>
-      </c>
+      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
@@ -9277,9 +8547,7 @@
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
-      <c r="G353" t="n">
-        <v>0</v>
-      </c>
+      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
@@ -9301,9 +8569,7 @@
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr"/>
-      <c r="G354" t="n">
-        <v>0</v>
-      </c>
+      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
@@ -9325,9 +8591,7 @@
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr"/>
-      <c r="G355" t="n">
-        <v>0</v>
-      </c>
+      <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
@@ -9349,9 +8613,7 @@
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr"/>
-      <c r="G356" t="n">
-        <v>0</v>
-      </c>
+      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
@@ -9373,9 +8635,7 @@
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr"/>
-      <c r="G357" t="n">
-        <v>0</v>
-      </c>
+      <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
@@ -9397,9 +8657,7 @@
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" t="n">
-        <v>0</v>
-      </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
@@ -9421,9 +8679,7 @@
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr"/>
-      <c r="G359" t="n">
-        <v>0</v>
-      </c>
+      <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
@@ -9445,9 +8701,7 @@
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr"/>
-      <c r="G360" t="n">
-        <v>0</v>
-      </c>
+      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr"/>
@@ -9469,9 +8723,7 @@
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
-      <c r="G361" t="n">
-        <v>0</v>
-      </c>
+      <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr"/>
@@ -9493,9 +8745,7 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="n">
-        <v>0</v>
-      </c>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
@@ -9517,9 +8767,7 @@
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="n">
-        <v>0</v>
-      </c>
+      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
@@ -9541,9 +8789,7 @@
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
-      <c r="G364" t="n">
-        <v>0</v>
-      </c>
+      <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
@@ -9565,9 +8811,7 @@
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr"/>
@@ -9589,9 +8833,7 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" t="n">
-        <v>0</v>
-      </c>
+      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr"/>
@@ -9613,9 +8855,7 @@
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
-      <c r="G367" t="n">
-        <v>0</v>
-      </c>
+      <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr"/>
@@ -9637,9 +8877,7 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" t="n">
-        <v>0</v>
-      </c>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
@@ -9661,9 +8899,7 @@
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr"/>
-      <c r="G369" t="n">
-        <v>0</v>
-      </c>
+      <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
@@ -9685,9 +8921,7 @@
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
-      <c r="G370" t="n">
-        <v>0</v>
-      </c>
+      <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr"/>
@@ -9709,9 +8943,7 @@
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="n">
-        <v>0</v>
-      </c>
+      <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr"/>
@@ -9733,9 +8965,7 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" t="n">
-        <v>0</v>
-      </c>
+      <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
@@ -9757,9 +8987,7 @@
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr"/>
-      <c r="G373" t="n">
-        <v>0</v>
-      </c>
+      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
@@ -9781,9 +9009,7 @@
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr"/>
-      <c r="G374" t="n">
-        <v>0</v>
-      </c>
+      <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr"/>
       <c r="J374" t="inlineStr"/>
@@ -9805,9 +9031,7 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" t="n">
-        <v>0</v>
-      </c>
+      <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
@@ -9829,9 +9053,7 @@
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="n">
-        <v>0</v>
-      </c>
+      <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
@@ -9853,9 +9075,7 @@
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="n">
-        <v>0</v>
-      </c>
+      <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
@@ -9877,9 +9097,7 @@
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr"/>
-      <c r="G378" t="n">
-        <v>0</v>
-      </c>
+      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
@@ -9901,9 +9119,7 @@
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="n">
-        <v>0</v>
-      </c>
+      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
@@ -9925,9 +9141,7 @@
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
-      <c r="G380" t="n">
-        <v>0</v>
-      </c>
+      <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
@@ -9949,9 +9163,7 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr"/>
-      <c r="G381" t="n">
-        <v>0</v>
-      </c>
+      <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
@@ -9973,9 +9185,7 @@
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
-      <c r="G382" t="n">
-        <v>0</v>
-      </c>
+      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
@@ -9997,9 +9207,7 @@
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
-      <c r="G383" t="n">
-        <v>0</v>
-      </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
@@ -10021,9 +9229,7 @@
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
-      <c r="G384" t="n">
-        <v>0</v>
-      </c>
+      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
@@ -10045,9 +9251,7 @@
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
-      <c r="G385" t="n">
-        <v>0</v>
-      </c>
+      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
@@ -10069,9 +9273,7 @@
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
-      <c r="G386" t="n">
-        <v>0</v>
-      </c>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
@@ -10093,9 +9295,7 @@
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
-      <c r="G387" t="n">
-        <v>0</v>
-      </c>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
@@ -10117,9 +9317,7 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" t="n">
-        <v>0</v>
-      </c>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
@@ -10141,9 +9339,7 @@
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
-      <c r="G389" t="n">
-        <v>0</v>
-      </c>
+      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr"/>
@@ -10165,9 +9361,7 @@
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" t="n">
-        <v>0</v>
-      </c>
+      <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr"/>
@@ -10189,9 +9383,7 @@
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr"/>
-      <c r="G391" t="n">
-        <v>0</v>
-      </c>
+      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr"/>
@@ -10213,9 +9405,7 @@
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
-      <c r="G392" t="n">
-        <v>0</v>
-      </c>
+      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr"/>
@@ -10237,9 +9427,7 @@
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
-      <c r="G393" t="n">
-        <v>0</v>
-      </c>
+      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr"/>
@@ -10261,9 +9449,7 @@
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr"/>
-      <c r="G394" t="n">
-        <v>0</v>
-      </c>
+      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr"/>
@@ -10285,9 +9471,7 @@
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr"/>
-      <c r="G395" t="n">
-        <v>0</v>
-      </c>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr"/>
@@ -10309,9 +9493,7 @@
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
-      <c r="G396" t="n">
-        <v>0</v>
-      </c>
+      <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr"/>
@@ -10333,9 +9515,7 @@
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr"/>
-      <c r="G397" t="n">
-        <v>0</v>
-      </c>
+      <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr"/>
@@ -10357,9 +9537,7 @@
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
-      <c r="G398" t="n">
-        <v>0</v>
-      </c>
+      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr"/>
@@ -10381,9 +9559,7 @@
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
-      <c r="G399" t="n">
-        <v>0</v>
-      </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr"/>
@@ -10405,9 +9581,7 @@
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr"/>
-      <c r="G400" t="n">
-        <v>0</v>
-      </c>
+      <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
@@ -10429,9 +9603,7 @@
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr"/>
-      <c r="G401" t="n">
-        <v>0</v>
-      </c>
+      <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
@@ -10453,9 +9625,7 @@
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr"/>
-      <c r="G402" t="n">
-        <v>0</v>
-      </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr"/>
@@ -10477,9 +9647,7 @@
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
-      <c r="G403" t="n">
-        <v>0</v>
-      </c>
+      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr"/>
@@ -10501,9 +9669,7 @@
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
-      <c r="G404" t="n">
-        <v>0</v>
-      </c>
+      <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr"/>
@@ -10525,9 +9691,7 @@
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
-      <c r="G405" t="n">
-        <v>0</v>
-      </c>
+      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr"/>
@@ -10549,9 +9713,7 @@
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr"/>
-      <c r="G406" t="n">
-        <v>0</v>
-      </c>
+      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr"/>
@@ -10573,9 +9735,7 @@
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr"/>
-      <c r="G407" t="n">
-        <v>0</v>
-      </c>
+      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr"/>
@@ -10597,9 +9757,7 @@
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr"/>
-      <c r="G408" t="n">
-        <v>0</v>
-      </c>
+      <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr"/>
@@ -10621,9 +9779,7 @@
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
-      <c r="G409" t="n">
-        <v>0</v>
-      </c>
+      <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
@@ -10645,9 +9801,7 @@
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr"/>
-      <c r="G410" t="n">
-        <v>0</v>
-      </c>
+      <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr"/>
@@ -10669,9 +9823,7 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr"/>
-      <c r="G411" t="n">
-        <v>0</v>
-      </c>
+      <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr"/>
@@ -10693,9 +9845,7 @@
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr"/>
-      <c r="G412" t="n">
-        <v>0</v>
-      </c>
+      <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
@@ -10717,9 +9867,7 @@
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
-      <c r="G413" t="n">
-        <v>0</v>
-      </c>
+      <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr"/>
@@ -10741,9 +9889,7 @@
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr"/>
-      <c r="G414" t="n">
-        <v>0</v>
-      </c>
+      <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr"/>
@@ -10765,9 +9911,7 @@
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>0</v>
-      </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr"/>
@@ -10789,9 +9933,7 @@
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
-      <c r="G416" t="n">
-        <v>0</v>
-      </c>
+      <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr"/>
@@ -10813,9 +9955,7 @@
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr"/>
-      <c r="G417" t="n">
-        <v>0</v>
-      </c>
+      <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr"/>
@@ -10837,9 +9977,7 @@
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr"/>
-      <c r="G418" t="n">
-        <v>0</v>
-      </c>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr"/>
@@ -10861,9 +9999,7 @@
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr"/>
-      <c r="G419" t="n">
-        <v>0</v>
-      </c>
+      <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
@@ -10885,9 +10021,7 @@
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
-      <c r="G420" t="n">
-        <v>0</v>
-      </c>
+      <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J420"/>
+  <dimension ref="A1:J443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:31:15</t>
+          <t>2026-05-20 12:05:25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:32:07</t>
+          <t>2026-05-20 12:06:07</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -532,17 +532,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-09 16:32:47</t>
+          <t>2026-05-20 12:06:47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-09 16:34:09</t>
+          <t>2026-05-20 12:07:15</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -563,28 +563,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-09 17:08:05</t>
+          <t>2026-05-20 12:07:55</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-09 17:09:07</t>
+          <t>2026-05-20 12:08:51</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
     </row>
@@ -604,17 +608,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-09 17:09:47</t>
+          <t>2026-05-20 12:09:31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-09 17:10:43</t>
+          <t>2026-05-20 12:10:31</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -635,28 +639,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-09 17:11:23</t>
+          <t>2026-05-20 12:11:11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-09 17:12:25</t>
+          <t>2026-05-20 12:12:11</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=31.2%)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -676,17 +684,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-09 17:13:20</t>
+          <t>2026-05-20 12:12:51</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-09 17:14:14</t>
+          <t>2026-05-20 12:13:21</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -712,17 +720,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-09 17:14:55</t>
+          <t>2026-05-20 12:14:01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-09 17:15:35</t>
+          <t>2026-05-20 12:14:28</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -738,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MiuMiu粉漾女士淡香氛50ml</t>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -748,17 +756,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-09 17:16:15</t>
+          <t>2026-05-20 12:15:08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-09 17:17:09</t>
+          <t>2026-05-20 12:16:58</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -766,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>nan；规格不匹配；品名相似不足(ratio=33.3%)</t>
+          <t>nan；规格不匹配；品名相似不足(ratio=40.0%)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -778,7 +786,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+          <t>NARS超方瓶粉底液L4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -788,17 +796,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-09 17:17:49</t>
+          <t>2026-05-20 12:17:38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-09 17:19:01</t>
+          <t>2026-05-20 12:18:32</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -806,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>nan；规格不匹配；品名相似不足(ratio=40.0%)</t>
+          <t>nan；规格不匹配</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -818,7 +826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NARS 超方瓶-L2</t>
+          <t>NARS 超方瓶粉底液 L3#</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -828,17 +836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-05-09 17:19:41</t>
+          <t>2026-05-20 12:19:12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-09 17:20:07</t>
+          <t>2026-05-20 12:19:46</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -854,7 +862,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>NARS 超方瓶粉底液#L1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,12 +877,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-05-09 17:20:47</t>
+          <t>2026-05-20 14:02:25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-09 17:21:18</t>
+          <t>2026-05-20 14:03:18</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -890,7 +898,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NARS 超方瓶粉底液 L3#</t>
+          <t>NARS 粉底液 LO色</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -905,12 +913,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05-09 17:21:58</t>
+          <t>2026-05-20 14:03:58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-09 17:22:51</t>
+          <t>2026-05-20 14:04:30</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -926,7 +934,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NARS 超方瓶粉底液#L1</t>
+          <t>NARS纳斯定妆散粉</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -941,12 +949,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-05-09 17:23:31</t>
+          <t>2026-05-20 14:05:10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-09 17:24:18</t>
+          <t>2026-05-20 14:06:15</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -962,12 +970,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NARS 粉底液 LO色</t>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -977,18 +985,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-05-09 17:24:58</t>
+          <t>2026-05-20 14:06:56</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-09 17:25:25</t>
+          <t>2026-05-20 14:08:04</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=27.3%)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
     </row>
@@ -998,12 +1010,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NARS纳斯定妆散粉</t>
+          <t>NARS 遮瑕膏 VANILLA色号</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1013,18 +1025,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-05-09 17:26:05</t>
+          <t>2026-05-20 14:08:44</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-09 17:26:54</t>
+          <t>2026-05-20 14:09:35</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nan；品名相似不足(ratio=10.0%)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
     </row>
@@ -1034,12 +1050,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+          <t>NARS5894蜜粉饼10G</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1049,22 +1065,18 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-05-09 17:28:55</t>
+          <t>2026-05-20 14:10:15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-09 17:29:48</t>
+          <t>2026-05-20 14:11:09</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>nan；规格不匹配；品名相似不足(ratio=27.3%)</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
     </row>
@@ -1074,7 +1086,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NARS 遮瑕膏 VANILLA色号</t>
+          <t>NARS空气唇釉686 lose control</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1089,12 +1101,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-09 17:30:28</t>
+          <t>2026-05-20 14:11:49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:18</t>
+          <t>2026-05-20 14:12:56</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1102,7 +1114,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>nan；品名相似不足(ratio=10.0%)</t>
+          <t>nan；规格不匹配；品名相似不足(ratio=35.7%)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1114,7 +1126,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NARS5894蜜粉饼10G</t>
+          <t>NARS空气唇釉thrust</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1129,12 +1141,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-09 17:31:58</t>
+          <t>2026-05-20 14:13:36</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-09 17:32:53</t>
+          <t>2026-05-20 14:14:20</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1150,12 +1162,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NARS空气唇釉686 lose control</t>
+          <t>NARS细管101 NO ANGEL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1165,22 +1177,18 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-09 17:33:33</t>
+          <t>2026-05-20 14:15:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-09 17:34:28</t>
+          <t>2026-05-20 14:15:48</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>nan；规格不匹配；品名相似不足(ratio=35.7%)</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
     </row>
@@ -1190,7 +1198,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NARS空气唇釉thrust</t>
+          <t>NARS细管116 START ME UP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1205,12 +1213,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-09 17:35:08</t>
+          <t>2026-05-20 14:16:28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-09 17:36:00</t>
+          <t>2026-05-20 14:17:27</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1226,7 +1234,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NARS细管101 NO ANGEL</t>
+          <t>NARS细管133 TOO HOT TO HOLD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1236,17 +1244,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-09 17:36:40</t>
+          <t>2026-05-20 14:20:01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-09 17:37:29</t>
+          <t>2026-05-20 14:20:47</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1262,7 +1270,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NARS细管116 START ME UP</t>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1272,17 +1280,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3B6F6AE7SX2MCMB9</t>
+          <t>IVHEGYKJJJVKCIBY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-09 17:38:09</t>
+          <t>2026-05-20 14:21:27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-09 17:38:41</t>
+          <t>2026-05-20 14:22:26</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1298,18 +1306,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NARS细管133 TOO HOT TO HOLD</t>
+          <t>SK2 神仙水230ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:24:19</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:25:21</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -1320,19 +1342,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
+          <t>SK2大红瓶滋润面霜100g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:26:02</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:26:55</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
     </row>
@@ -1342,18 +1382,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+          <t>SK2神仙水330ML</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:27:35</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:28:41</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -1364,18 +1418,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SK2 神仙水230ml</t>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:29:21</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:30:29</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -1386,19 +1454,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润面霜100g</t>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:31:09</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:31:43</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
     </row>
@@ -1408,18 +1494,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK2神仙水330ML</t>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:32:23</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:33:21</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -1430,18 +1530,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SK-II 男士保湿焕活洁面霜120g</t>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:34:01</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:34:55</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -1452,18 +1566,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK-II 男士焕活护肤精华露 230ml</t>
+          <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:35:35</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:36:35</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -1474,18 +1602,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SK-II 小银瓶淡斑精华露75ml</t>
+          <t>TF白麝香 100ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:37:15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:38:20</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1496,18 +1638,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SK-II 小银瓶淡斑精华露75ml</t>
+          <t>TF黑管哑光16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:39:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:39:57</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -1518,18 +1674,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
+          <t>TF黑金唇釉123</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:41:57</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:42:58</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -1540,19 +1710,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TF白麝香 100ml</t>
+          <t>TF幻魅四色眼影盘#41 Peach Dawn桃色晨曦盘</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:43:38</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:44:32</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
     </row>
@@ -1562,18 +1750,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TF黑管哑光16</t>
+          <t>TF幻魅四色眼影盘#GOLDEN MINK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:45:13</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:45:39</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -1584,18 +1786,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TF黑金唇釉123</t>
+          <t>TF镜面唇蜜17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:46:19</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:47:19</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -1606,19 +1822,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TF幻魅四色眼影盘#41 Peach Dawn桃色晨曦盘</t>
+          <t>TF汤姆福特 乌木沉香 100ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:47:59</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:49:01</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -1628,18 +1862,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TF幻魅四色眼影盘#GOLDEN MINK</t>
+          <t>TF细黑管52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:49:41</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:50:09</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -1650,19 +1898,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TF镜面唇蜜17</t>
+          <t>VAPE未來驅蚊液海藍柑橘噴霧200ml</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:52:08</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:53:37</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=11.1%)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
     </row>
@@ -1672,18 +1938,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TF汤姆福特 乌木沉香 100ml</t>
+          <t>YSL 细管丝绒纯口红 小黑条 316#</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:54:17</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:54:43</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -1694,18 +1974,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TF细黑管52</t>
+          <t>YSL黑管唇釉416</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:55:23</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:56:11</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -1716,18 +2010,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VAPE未來驅蚊液海藍柑橘噴霧200ml</t>
+          <t>YSL黑管唇釉416</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:56:51</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:57:58</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -1738,18 +2046,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YSL 细管丝绒纯口红 小黑条 316#</t>
+          <t>YSL反转巴黎浓香香水50ml</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:58:38</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:59:06</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -1760,18 +2082,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YSL黑管唇釉416</t>
+          <t>YSL粉气垫替换芯B10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:59:46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:00:39</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -1782,18 +2118,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YSL黑管唇釉416</t>
+          <t>YSL粉气垫B10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:01:19</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:02:07</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -1804,18 +2154,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YSL反转巴黎浓香香水50ml</t>
+          <t>YSL粉气垫替换芯br20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:02:47</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:03:27</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -1826,19 +2190,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YSL粉气垫替换芯B10</t>
+          <t>YSL黑鸦片浓香50ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:04:07</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:05:14</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
     </row>
@@ -1848,18 +2230,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YSL粉气垫B10</t>
+          <t>YSL口红8B</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:05:54</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:07:02</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -1870,18 +2266,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YSL粉气垫替换芯br20</t>
+          <t>YSL皮革气垫B20替换芯新款</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:09:03</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:09:59</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -1892,19 +2302,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YSL黑鸦片浓香50ml</t>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:10:39</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:12:09</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=30.8%)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -1914,19 +2342,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YSL口红8B</t>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:12:49</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:14:06</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=38.5%)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
     </row>
@@ -1936,18 +2382,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YSL皮革气垫B20替换芯新款</t>
+          <t>YSL细管小金条 #1966</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:14:46</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:15:41</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -1958,19 +2418,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+          <t>YSL自由之水浓香型30ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:16:21</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:17:42</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
     </row>
@@ -1980,18 +2458,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+          <t>YSL自由之水浓香50ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:18:22</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:18:52</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -2002,18 +2494,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YSL细管小金条 #1966</t>
+          <t>YSL自由之水浓香90ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:19:32</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:20:22</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -2024,18 +2530,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YSL自由之水浓香型30ml</t>
+          <t>阿玛尼 寄情男士淡香水100ml 新版</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:21:02</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:22:00</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -2046,18 +2566,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YSL自由之水浓香50ml</t>
+          <t>阿玛尼大师蓝标粉底液1.5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:22:40</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:23:32</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -2068,18 +2602,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YSL自由之水浓香90ml</t>
+          <t>阿玛尼红管唇釉206#</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:24:12</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:25:15</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -2090,12 +2638,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>阿玛尼 寄情男士淡香水100ml 新版</t>
+          <t>阿玛尼红管唇釉405-24年</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2112,12 +2660,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>阿玛尼大师蓝标粉底液1.5</t>
+          <t>阿玛尼红气垫替换芯2#-24年</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2134,12 +2682,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>阿玛尼红管唇釉206#</t>
+          <t>阿玛尼权力粉底液3号</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2156,12 +2704,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>阿玛尼红管唇釉405-24年</t>
+          <t>阿玛尼臻致丝绒哑光唇釉#214</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2178,12 +2726,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>阿玛尼红气垫替换芯2#-24年</t>
+          <t xml:space="preserve">阿玛尼挚爱哑光唇膏#400 </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2200,12 +2748,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>阿玛尼权力粉底液3号</t>
+          <t>爱马仕尼罗河淡香30ml</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2222,12 +2770,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>阿玛尼臻致丝绒哑光唇釉#214</t>
+          <t>芭比波朗 密集修护菁华妆前乳 40ml</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2244,12 +2792,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">阿玛尼挚爱哑光唇膏#400 </t>
+          <t>芭比波朗 维他命橘子面霜 50ml</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2266,12 +2814,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>爱马仕尼罗河淡香30ml</t>
+          <t>芭比波朗月光石眼影</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2288,12 +2836,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>芭比波朗 密集修护菁华妆前乳 40ml</t>
+          <t>百瑞德无人区玫瑰50ML</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2310,12 +2858,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>芭比波朗 维他命橘子面霜 50ml</t>
+          <t>城野医生美白淡斑精华18g</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2332,12 +2880,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>芭比波朗月光石眼影</t>
+          <t>黛珂 多重防護素顏霜35g SPF50+/PA++++ #10 新版</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2354,12 +2902,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>百瑞德无人区玫瑰50ML</t>
+          <t>黛珂 防晒防水版60g</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2376,12 +2924,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>城野医生美白淡斑精华1</t>
+          <t>黛珂 植物韵律清爽乳200ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2398,12 +2946,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>黛珂 多重防護素顏霜35g SPF50+/PA++++ #10 新版</t>
+          <t>黛珂 植物韵律清爽水200ml</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2420,12 +2968,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>黛珂 防晒防水版60g</t>
+          <t>黛珂AQ白檀乳液200ml清爽型</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2442,12 +2990,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>黛珂 植物韵律清爽乳200ml</t>
+          <t>黛珂AQ白檀水200ml清爽型</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2464,12 +3012,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>黛珂 植物韵律清爽水200ml</t>
+          <t>黛珂AQ舒活白檀美白乳液200ml</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2486,12 +3034,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>黛珂智密紧颜美白清爽乳液 200ml</t>
+          <t>黛珂AQ舒活滋润化妆水200ml</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2508,12 +3056,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>黛珂AQ白檀乳液200ml清爽型</t>
+          <t>黛珂AQ舒活滋润乳液200ml</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2530,12 +3078,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>黛珂AQ白檀水200ml清爽型</t>
+          <t>黛珂牛油果乳液 300ml</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2552,12 +3100,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>黛珂AQ舒活白檀美白乳液200ml</t>
+          <t>黛珂牛油果乳液150ml</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2574,12 +3122,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>黛珂AQ舒活滋润化妆水200ml</t>
+          <t>黛珂沁活晶澈润肤精华水200ml</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2596,12 +3144,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>黛珂AQ舒活滋润乳液200ml</t>
+          <t>黛珂散粉01 24年新版</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2618,12 +3166,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液 300ml</t>
+          <t>黛珂散粉光肌00 24年新版</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2640,12 +3188,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液150ml</t>
+          <t>黛珂紫苏水 300ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2662,12 +3210,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>黛珂沁活晶澈润肤精华水200ml</t>
+          <t>黛珂紫苏水150ml</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2684,12 +3232,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>黛珂散粉01 24年新版</t>
+          <t>德美乐嘉多维面膜涂抹面膜75ml</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2706,12 +3254,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>黛珂散粉光肌00 24年新版</t>
+          <t>费列罗榛果巧克力制品T24</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2728,12 +3276,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>黛珂紫苏水 300ml</t>
+          <t>拱辰享洁面180ml</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2750,12 +3298,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>黛珂紫苏水150ml</t>
+          <t>古驰花悦绽放女士浓香50ml</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2772,12 +3320,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>德美乐嘉多维面膜涂抹面膜75ml</t>
+          <t>古驰金管217哑光</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -2794,12 +3342,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>费列罗榛果巧克力制品T24</t>
+          <t>古驰金管哑光口红208#</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2816,12 +3364,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>拱辰享洁面180ml</t>
+          <t>古驰绮梦香草兰香型30ml</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2838,12 +3386,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士浓香50ml</t>
+          <t>古驰细管口红#25*</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2860,12 +3408,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>古驰金管217哑光</t>
+          <t>古驰倾色绒雾唇膏505（金色短管）</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2882,12 +3430,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>古驰金管哑光口红208#</t>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2904,12 +3452,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>古驰绮梦香草兰香型30ml</t>
+          <t>古驰竹韵淡香50ml</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2926,12 +3474,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>古驰细管口红#25*</t>
+          <t>古驰罪爱男香50ml</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2948,12 +3496,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>古驰倾色绒雾唇膏505（金色短管）</t>
+          <t>海蓝之谜唇膜9g</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2970,12 +3518,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>古驰倾色云雾唇釉505（红色长管）</t>
+          <t>海蓝之谜精粹水 150ml 新版</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2992,18 +3540,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>古驰竹韵淡香50ml</t>
+          <t>海蓝之谜精粹水150ml</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:56:16</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:57:41</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
@@ -3014,18 +3576,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>古驰罪爱男香50ml</t>
+          <t>海蓝之谜精华面霜60ml</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:58:21</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:58:52</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -3036,18 +3612,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>海蓝之谜唇膜9g</t>
+          <t>海蓝之谜绿眼霜15ml</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:59:32</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:00:02</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -3058,18 +3648,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>海蓝之谜精粹水 150ml 新版</t>
+          <t>海蓝之谜面霜100ml</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:00:42</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:01:09</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -3080,18 +3684,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>海蓝之谜精粹水150ml</t>
+          <t>海蓝之谜气垫1号</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:01:49</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:02:37</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -3102,18 +3720,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>海蓝之谜精华面霜60ml</t>
+          <t>赫莲娜 黑绷带50ml</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:03:17</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:04:18</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
@@ -3124,18 +3756,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>海蓝之谜绿眼霜15ml</t>
+          <t>赫莲娜黑绷带100ml</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:04:58</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:05:56</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -3146,19 +3792,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>海蓝之谜面霜100ml</t>
+          <t>赫莲娜黑绷带活颜修护舒缓晚霜115ML</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:06:37</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:07:52</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
     </row>
@@ -3168,18 +3832,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>海蓝之谜气垫1号</t>
+          <t>赫莲娜活颜修护眼霜 15ml</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:08:32</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:09:33</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -3190,18 +3868,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>赫莲娜 黑绷带50ml</t>
+          <t>赫莲娜绿宝瓶精华 按压款100ml</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:10:13</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:10:44</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -3212,18 +3904,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>赫莲娜黑绷带100ml</t>
+          <t>赫莲娜小露珠精粹露200ml新款</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:12:44</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:13:54</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
@@ -3234,18 +3940,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>赫莲娜黑绷带活颜修护舒缓晚霜115ML</t>
+          <t>后拱辰享气韵生水150ml</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:14:35</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:15:03</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
@@ -3256,18 +3976,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>赫莲娜活颜修护眼霜 15ml</t>
+          <t>后拱辰享水妍洁面180ml</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:15:44</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:16:26</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
@@ -3278,18 +4012,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶精华 按压款100ml</t>
+          <t>后拱辰享水沄赋活保湿水150ml</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:17:06</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:17:56</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
@@ -3300,18 +4048,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>赫莲娜小露珠精粹露200ml新款</t>
+          <t>后拱辰享雪美白水150ml</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:18:36</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:19:07</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
@@ -3322,18 +4084,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>后拱辰享气韵生水150ml</t>
+          <t>后津率享洁面180ml</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:19:47</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:20:15</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
@@ -3344,18 +4120,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>后拱辰享水妍洁面180ml</t>
+          <t>后津率享平衡水150ml</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:20:55</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:21:21</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
@@ -3366,18 +4156,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>后拱辰享水沄赋活保湿水150ml</t>
+          <t>后天气丹PRO水150ML</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:22:01</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:22:28</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
@@ -3388,18 +4192,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>后拱辰享雪美白水150ml</t>
+          <t>后拱辰享美白洗面奶 180ml</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:23:08</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:24:15</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -3410,18 +4228,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>后津率享洁面180ml</t>
+          <t>纪梵希 粉丝绒N27</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3B6F6AE7SX2MCMB9</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:24:55</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:25:37</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
@@ -3432,12 +4264,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>后津率享平衡水150ml</t>
+          <t>纪梵希 红丝绒口红#N36</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3454,12 +4286,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>后天气丹PRO水150ML</t>
+          <t>纪梵希 红丝绒口红#N37</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3476,12 +4308,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>后雪玉凝美白洗面奶 180ml</t>
+          <t>纪梵希 小粉皮口红#N333</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3498,12 +4330,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>纪梵希 粉丝绒N27</t>
+          <t>纪梵希 小羊皮 N306</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -3520,12 +4352,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>纪梵希 红丝绒口红#N36</t>
+          <t>纪梵希四宫格散粉1号色</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3542,12 +4374,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>纪梵希 红丝绒口红#N37</t>
+          <t>娇兰第四代复原蜜精华50ml</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3564,12 +4396,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>纪梵希 小粉皮口红#N333</t>
+          <t>娇韵诗弹簧水200ml</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3586,12 +4418,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>纪梵希 小羊皮 N306</t>
+          <t>娇韵诗光芒小瓷瓶精华50ml</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -3608,12 +4440,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色</t>
+          <t>娇韵诗双萃精华50ml九代新版</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -3630,12 +4462,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>娇兰第四代复原蜜精华50ml</t>
+          <t>娇韵诗双萃精华清爽50ML</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3652,12 +4484,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>娇韵诗弹簧水200ml</t>
+          <t>娇韵诗透亮焕白淡斑乳液75mL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -3674,12 +4506,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>娇韵诗光芒小瓷瓶精华50ml</t>
+          <t>科颜氏白泥面膜125ml 24款</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -3696,12 +4528,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>娇韵诗双萃精华50ml九代新版</t>
+          <t>科颜氏 高保湿面霜125ml 滋润</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3718,12 +4550,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>娇韵诗双萃精华清爽50ML</t>
+          <t>科颜氏 金盏花洁面啫喱230ml</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3740,12 +4572,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>娇韵诗透亮焕白淡斑乳液75mL</t>
+          <t>科颜氏 金盏花面霜100ml</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3762,12 +4594,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>科颜氏白泥面膜125ml 24款</t>
+          <t>科颜氏 金盏花面霜50ml</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3784,12 +4616,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>科颜氏 高保湿面霜125ml 滋润</t>
+          <t>科颜氏 金盏花爽肤水250ml</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3806,12 +4638,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>科颜氏 金盏花洁面啫喱230ml</t>
+          <t>科颜氏 金盏花植物精华化妆水500ml</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -3828,12 +4660,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>科颜氏 金盏花面霜100ml</t>
+          <t>科颜氏 美白淡斑精华100ml</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3850,12 +4682,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>科颜氏 金盏花面霜50ml</t>
+          <t>科颜氏淡斑精华115ml</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -3872,12 +4704,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>科颜氏 金盏花爽肤水250ml</t>
+          <t>科颜氏高保湿霜125ml 清爽</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -3894,12 +4726,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>科颜氏 金盏花植物精华化妆水500ml</t>
+          <t>科颜氏高保湿滋润面霜50ml滋润</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3916,12 +4748,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>科颜氏 美白淡斑精华100ml</t>
+          <t>科颜氏男士洁面啫喱250ml</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3938,12 +4770,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>科颜氏淡斑精华115ml</t>
+          <t>蔻依北国雪松浓香水50ml</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3960,19 +4792,37 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>科颜氏高保湿霜125ml 清爽</t>
+          <t>拉夫劳伦地球淡香氛 100ml</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:42:58</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:43:58</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
     </row>
@@ -3982,19 +4832,37 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>科颜氏高保湿滋润面霜50ml滋润</t>
+          <t>拉夫劳伦地球淡香氛 40ml</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:44:38</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:45:33</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
     </row>
@@ -4004,19 +4872,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>科颜氏男士洁面啫喱250ml</t>
+          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 100ml</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:46:13</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:46:59</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
     </row>
@@ -4026,19 +4912,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>蔻依北国雪松浓香水50ml</t>
+          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 40ml</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:47:39</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:48:38</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
     </row>
@@ -4048,19 +4952,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球淡香氛 100ml</t>
+          <t>拉夫劳伦地球系列淡香氛 摩洛哥橙花 40ml</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:49:18</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:50:18</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=40.0%)</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
     </row>
@@ -4070,19 +4992,37 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球淡香氛 40ml</t>
+          <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 100ml</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:50:58</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:51:52</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>nan；规格不匹配；品名相似不足(ratio=41.7%)</t>
+        </is>
+      </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
     </row>
@@ -4092,19 +5032,37 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 100ml</t>
+          <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 40ml</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:52:32</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:53:34</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=16.7%)</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
     </row>
@@ -4114,19 +5072,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 40ml</t>
+          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:54:14</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:55:14</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
     </row>
@@ -4136,19 +5112,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 摩洛哥橙花 40ml</t>
+          <t>拉夫劳伦地球系列香氛 澳洲檀木 40ml</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>未采集</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>IVHEGYKJJJVKCIBY</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:55:54</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:56:40</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>nan；品牌不一致；规格不匹配</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
     </row>
@@ -4158,12 +5152,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 100ml</t>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4180,12 +5174,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 40ml</t>
+          <t>拉夫劳伦俱乐部香水淡香型 30ML</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4202,12 +5196,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
+          <t>欧珑无极乌龙护手霜30ML</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4224,12 +5218,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 40ml</t>
+          <t>莱珀妮反重力精华50ml</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4246,12 +5240,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+          <t>兰蔻 持妆粉底液 PO-01 30ml</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4268,12 +5262,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 30ML</t>
+          <t xml:space="preserve">兰蔻 极光乳液净澈焕肤亮白乳液 75ml </t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4290,12 +5284,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>欧珑无极乌龙护手霜30ML</t>
+          <t>兰蔻 极光水250ML新款</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4312,12 +5306,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>莱珀妮反重力精华50ml</t>
+          <t>兰蔻二代精华肌底液115ml</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4334,12 +5328,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>兰蔻 持妆粉底液 PO-01 30ml</t>
+          <t>兰蔻粉水400ml 旧版</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4356,12 +5350,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">兰蔻 极光乳液净澈焕肤亮白乳液 75ml </t>
+          <t>兰蔻粉水400ml 新版</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4378,12 +5372,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>兰蔻 极光水250ML新款</t>
+          <t>兰蔻第二代肌底液100ml</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4400,12 +5394,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>兰蔻二代精华肌底液115ml</t>
+          <t>兰蔻极光洁面乳125ml</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4422,12 +5416,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>兰蔻粉水400ml 旧版</t>
+          <t>兰蔻极光美白精华50ml 新款</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -4444,12 +5438,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>兰蔻粉水400ml 新版</t>
+          <t>兰蔻菁纯丝绒雾面唇膏200#</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -4466,12 +5460,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>兰蔻第二代肌底液100ml</t>
+          <t>兰蔻奇迹香水30ml</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -4488,12 +5482,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>兰蔻极光洁面乳125ml</t>
+          <t>兰蔻清爽防晒50ml 25款</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4510,12 +5504,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>兰蔻极光美白精华50ml 新款</t>
+          <t>兰蔻是我淡香水 50ml</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4532,12 +5526,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>兰蔻菁纯丝绒雾面唇膏200#</t>
+          <t>兰蔻小白管防晒乳50ml</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -4554,12 +5548,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>兰蔻奇迹香水30ml</t>
+          <t>兰蔻小黑瓶肌底液第二代100ml*2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -4576,12 +5570,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>兰蔻清爽防晒50ml 25款</t>
+          <t>兰蔻小黑瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -4598,12 +5592,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>兰蔻是我淡香水 50ml</t>
+          <t>兰蔻小蛮腰哑光296唇膏</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4620,12 +5614,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>兰蔻小白管防晒乳50ml</t>
+          <t>罗拉散粉经典款29G</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -4642,12 +5636,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>兰蔻小黑瓶肌底液第二代100ml*2</t>
+          <t>马丁马吉拉-慵懒周末100ml</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4664,12 +5658,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>兰蔻小黑瓶眼霜15ml</t>
+          <t>慕拉得塑颜修复A醇精华30ml</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4686,12 +5680,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>兰蔻小蛮腰哑光296唇膏</t>
+          <t>欧珑赤霞橘光护手霜30ML</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4708,12 +5702,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>欧珑淡香精  赤霞橘光 100ML</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4730,12 +5724,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>马丁马吉拉-慵懒周末100ml</t>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4752,12 +5746,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>欧珑淡香精 赤霞橘光 30ML</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4774,12 +5768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
+          <t>欧珑淡香精 情柚独钟 30ML</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -4796,12 +5790,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>欧珑淡香精  赤霞橘光 100ML</t>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -4818,12 +5812,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>欧珑淡香精  情柚独钟 100ML</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -4840,12 +5834,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4862,12 +5856,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>欧珑淡香精 赤霞橘光 30ML</t>
+          <t>倩碧 紫胖子卸妆膏125ml</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -4884,12 +5878,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
+          <t xml:space="preserve">倩碧小雏菊裸色阳光腮#05 </t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -4906,12 +5900,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>薇迪薇奇净颜美肌洁面乳</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -4928,12 +5922,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4950,12 +5944,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -4972,12 +5966,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>倩碧 紫胖子卸妆膏125ml</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -4994,12 +5988,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">倩碧小雏菊裸色阳光腮#05 </t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5016,12 +6010,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5038,12 +6032,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -5060,12 +6054,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>雅诗兰黛DW  2c0</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -5082,12 +6076,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -5104,12 +6098,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>伟博天然鱼油软胶囊120粒</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -5126,7 +6120,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5148,7 +6142,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5170,7 +6164,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5192,7 +6186,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5214,7 +6208,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>茵芙纱 三色遮瑕4.5g</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5236,7 +6230,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂安耐晒60ml新版</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5258,7 +6252,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+          <t>资生堂百优面霜 75ml</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5280,7 +6274,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>雅诗兰黛线雕精华50ml（新版）</t>
+          <t>资生堂蓝胖子150ml 新版</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5302,7 +6296,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+          <t>资生堂蓝胖子防晒50ml</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5324,7 +6318,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>雅诗兰黛智妍晚霜75ml</t>
+          <t>资生堂蓝胖子防晒50ml（新版）</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5346,7 +6340,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>茵芙纱 三色遮瑕4.5g</t>
+          <t>资生堂琉璃洁面125ml</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5368,7 +6362,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>资生堂安耐晒60ml新版</t>
+          <t>资生堂琉璃洁面50ml新版</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5390,7 +6384,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>资生堂百优面霜 75ml</t>
+          <t>资生堂琉璃爽肤水74ml新版</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5412,7 +6406,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子150ml 新版</t>
+          <t>资生堂男生爽肤水150ml</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5434,7 +6428,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子防晒50ml</t>
+          <t>资生堂男士洁面乳125ml</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5456,7 +6450,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子防晒50ml（新版）</t>
+          <t>资生堂男士乳液100ml</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5478,7 +6472,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>资生堂琉璃洁面125ml</t>
+          <t>资生堂悦微清爽水150ml（新版）</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5500,7 +6494,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>资生堂琉璃洁面50ml新版</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5522,7 +6516,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>资生堂琉璃爽肤水74ml新版</t>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5544,7 +6538,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>资生堂男生爽肤水150ml</t>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5566,7 +6560,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>资生堂男士洁面乳125ml</t>
+          <t>资生堂悦薇清爽乳100ml（新版）</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5588,7 +6582,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>资生堂男士乳液100ml</t>
+          <t>祖玛珑 蓝风铃香水100ml</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5610,7 +6604,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>资生堂悦微清爽水150ml（新版）</t>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5632,7 +6626,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
+          <t>阿玛尼大师蓝标粉底液2#</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5654,7 +6648,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>资生堂悦薇纯A小针管眼霜20ml</t>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5676,7 +6670,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>资生堂悦薇滋润乳100ml（新版）</t>
+          <t>阿玛尼权力PR0粉底30ml#3</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5698,7 +6692,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>资生堂悦薇清爽乳100ml（新版）</t>
+          <t>阿玛尼「大师」锁光粉底液#3</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5720,7 +6714,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>祖玛珑 蓝风铃香水100ml</t>
+          <t>阿玛尼气垫替换芯3号</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5742,7 +6736,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+          <t>兰蔻水唇釉275#</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5764,7 +6758,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>阿玛尼大师蓝标粉底液2#</t>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5786,7 +6780,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底 30m1#2</t>
+          <t>POLA 黑BA洁面</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5808,7 +6802,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底 30m1 #3</t>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5830,7 +6824,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>阿玛尼「大师」锁光粉底液#3</t>
+          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5852,7 +6846,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>阿玛尼气垫替换芯3号</t>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5874,7 +6868,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>兰蔻水唇釉275#</t>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5896,7 +6890,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>古驰绮梦栀子花香水50ml浓香型</t>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5918,7 +6912,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>POLA 黑BA洁面</t>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5940,7 +6934,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5962,7 +6956,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5984,7 +6978,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6006,7 +7000,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6028,7 +7022,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+          <t>SK2大红瓶面霜80g滋润</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6050,7 +7044,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6072,7 +7066,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
+          <t>雅诗兰黛红石榴洁面125ml</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6094,7 +7088,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6116,7 +7110,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6138,7 +7132,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>植村秀持久保湿定妆喷雾100ml</t>
+          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6160,7 +7154,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SK2大红瓶面霜80g滋润</t>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6182,7 +7176,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6204,7 +7198,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面125ml</t>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6226,7 +7220,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6248,7 +7242,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6270,7 +7264,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
+          <t>CK Man男士香水 50ml EDT</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6292,7 +7286,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -6314,7 +7308,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO百优面霜50ml</t>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6336,7 +7330,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6358,7 +7352,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6380,7 +7374,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>范思哲 追梦人男士淡香水 100ml EDT</t>
+          <t>娇韵诗 双萃眼霜 20ml</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6402,7 +7396,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>博柏利 新伦敦男士淡香水 50ml EDT</t>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6424,7 +7418,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CK Man男士香水 50ml EDT</t>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6446,7 +7440,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+          <t>娇韵诗 抚纹油 100ml</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6468,7 +7462,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6490,7 +7484,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+          <t>欧舒丹樱花护手霜三支装</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6512,7 +7506,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>古驰 竹韵女士香水浓香型50ml</t>
+          <t>欧舒丹乳木果身体乳250ml</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6534,7 +7528,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>娇韵诗 双萃眼霜 20ml</t>
+          <t>欧舒丹玫瑰身体乳250ml</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6556,7 +7550,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>娇韵诗 双萃新版第9代 75ml</t>
+          <t>海蓝之谜洁面125ml</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6578,7 +7572,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+          <t>CPB滋润洗面奶125ml</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6600,7 +7594,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>娇韵诗 抚纹油 100ml</t>
+          <t>CPB美白短管隔离30ml</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6622,7 +7616,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>娇韵诗 双萃新版第9代 30ml</t>
+          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6644,7 +7638,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>欧舒丹樱花护手霜三支装</t>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6666,7 +7660,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>欧舒丹乳木果身体乳250ml</t>
+          <t>圣罗兰爱心黑管唇釉620</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6688,7 +7682,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>欧舒丹玫瑰身体乳250ml</t>
+          <t>圣罗兰黑色皮革气垫B10</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6710,7 +7704,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>海蓝之谜洁面125ml</t>
+          <t>圣罗兰黑色皮革气垫替换装B10</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6732,7 +7726,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CPB滋润洗面奶125ml</t>
+          <t>兰蔻菁纯粉底液100</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6754,7 +7748,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CPB美白短管隔离30ml</t>
+          <t>SK2骨胶原乳液100g</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6776,7 +7770,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
+          <t>SK2清莹露230ml</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6798,7 +7792,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>红石榴面霜50ml 旧版</t>
+          <t>SK2立体修护眼霜15g两瓶装</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6820,7 +7814,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉620</t>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6842,7 +7836,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>圣罗兰黑色皮革气垫B10</t>
+          <t>碧欧泉男士水动力乳液100ml</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6864,7 +7858,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>圣罗兰黑色皮革气垫替换装B10</t>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6886,7 +7880,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>兰蔻菁纯粉底液100</t>
+          <t>圣罗兰女神逆龄粉底液B20</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6908,7 +7902,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SK2骨胶原乳液100g</t>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6930,7 +7924,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SK2清莹露230ml</t>
+          <t>兰蔻第三代肌底液100ml</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6952,7 +7946,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SK2立体修护眼霜15g两瓶装</t>
+          <t>衰败城市牛郎眼影</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6974,7 +7968,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6996,7 +7990,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>碧欧泉男士水动力乳液100ml</t>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -7018,7 +8012,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+          <t>爱马仕大地淡香水50ml</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -7040,7 +8034,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>圣罗兰女神逆龄粉底液B20</t>
+          <t>苏秘气垫1号</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -7062,7 +8056,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -7084,7 +8078,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>兰蔻第三代肌底液100ml</t>
+          <t>YSL圣罗兰夜皇后50ml</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7106,7 +8100,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>衰败城市牛郎眼影</t>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7128,7 +8122,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7150,7 +8144,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7172,7 +8166,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>爱马仕大地淡香水50ml</t>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7194,7 +8188,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>苏秘气垫1号</t>
+          <t>资生堂蓝胖子防晒50ml对装</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7216,7 +8210,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
+          <t xml:space="preserve">阿玛尼权力PR0粉底1.5 30ml </t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7238,7 +8232,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>YSL圣罗兰夜皇后50ml</t>
+          <t>兰蔻小黑瓶眼霜20ml</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7260,7 +8254,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+          <t>HR赫莲娜绿眼霜对装</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7282,7 +8276,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7304,7 +8298,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
+          <t>MAC无瑕粉底液N11 2.0</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7326,7 +8320,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+          <t>MAC无瑕粉底液N18 2.0</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7348,7 +8342,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子防晒50ml对装</t>
+          <t>MAC无瑕粉底液NC11 2.0</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7370,7 +8364,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t xml:space="preserve">阿玛尼权力PR0粉底1.5 30ml </t>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7392,7 +8386,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>兰蔻小黑瓶眼霜20ml</t>
+          <t>黛珂牛油果乳液300ml*2</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7414,7 +8408,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿眼霜对装</t>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7436,7 +8430,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
+          <t>GUCCI绮梦馥栀100ML</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7458,7 +8452,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N11 2.0</t>
+          <t>GUCCI花悦绽放100ML浓香</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7480,7 +8474,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N18 2.0</t>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7502,7 +8496,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7524,7 +8518,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
+          <t>GUCCI绮梦香草兰香100ml</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7546,7 +8540,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液300ml*2</t>
+          <t>GUCCI绮梦香草兰香50ml</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7568,7 +8562,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7590,7 +8584,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7612,7 +8606,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7634,7 +8628,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
+          <t>SK-II光子小灯泡精华露50ml</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7656,7 +8650,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
+          <t>SK-II晶致美肤乳液100g</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7678,7 +8672,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>SKII女士洗面奶120g/支</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7700,7 +8694,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香50ml</t>
+          <t>SK-II前男友面膜10片装</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7722,7 +8716,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+          <t>SK-II前男友面膜10片装</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7744,7 +8738,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+          <t>SKII大红瓶面霜80g清爽</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7766,7 +8760,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7788,7 +8782,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>SK-II光子小灯泡精华露50ml</t>
+          <t>后Whoo天气丹PRO乳110ML</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7810,7 +8804,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>SK-II晶致美肤乳液100g</t>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7832,7 +8826,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>SKII女士洗面奶120g/支</t>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7854,7 +8848,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
+          <t>SK-II小灯泡新版50ml</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7876,7 +8870,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
+          <t>SKII光子小灯泡75ml</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7898,7 +8892,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g清爽</t>
+          <t>SKII洁面油250ml</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7920,7 +8914,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>NARS空气唇釉GIPSY吉普赛</t>
+          <t>纪梵希粉丝绒N37</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7942,7 +8936,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>后Whoo天气丹PRO乳110ML</t>
+          <t>圣罗兰爱心黑管唇釉440</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7964,7 +8958,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7986,7 +8980,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+          <t>雅诗兰黛红石榴水200ml两支装</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -8008,7 +9002,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>SK-II小灯泡新版50ml</t>
+          <t>SK2小银瓶50ml两瓶装</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -8030,7 +9024,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>SKII光子小灯泡75ml</t>
+          <t>SK2大红瓶滋润面霜50g</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -8052,7 +9046,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
+          <t>馥蕾诗西柚香皂</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -8074,7 +9068,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>纪梵希粉丝绒N37</t>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8096,7 +9090,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉440</t>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -8118,7 +9112,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+          <t>馥蕾诗睡莲日霜50ml</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8140,7 +9134,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴水200ml两支装</t>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -8162,7 +9156,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>SK2小银瓶50ml两瓶装</t>
+          <t>馥蕾诗小苍兰香皂</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -8184,7 +9178,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润面霜50g</t>
+          <t>雅诗兰黛白金粉底液1W0</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -8206,7 +9200,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>馥蕾诗西柚香皂</t>
+          <t>馥蕾诗红茶精粹水250ml</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -8228,7 +9222,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>馥蕾诗玫瑰花瓣水400ml</t>
+          <t>雅诗兰黛白金粉底液1CO</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -8250,7 +9244,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>馥蕾诗红茶紧致面霜50ml</t>
+          <t>娇韵诗美白滋润水200ml</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -8272,7 +9266,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>馥蕾诗睡莲日霜50ml</t>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -8294,7 +9288,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -8316,7 +9310,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>馥蕾诗小苍兰香皂</t>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -8338,7 +9332,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>雅诗兰黛白金粉底液1W0</t>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -8360,7 +9354,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>馥蕾诗红茶精粹水250ml</t>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8382,7 +9376,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>雅诗兰黛白金粉底液1CO</t>
+          <t>科颜氏男士乳液125ml</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8404,7 +9398,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>娇韵诗美白滋润水200ml</t>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8426,7 +9420,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>娇韵诗焕颜紧致晚霜50ml</t>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8448,7 +9442,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+          <t>资生堂安耐晒90ml</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8470,7 +9464,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+          <t>安耐晒金钻高效防晒90ml</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8492,7 +9486,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8514,7 +9508,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>科颜氏男士乳液125ml</t>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8536,7 +9530,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8558,7 +9552,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8580,7 +9574,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>资生堂安耐晒90ml</t>
+          <t>阿玛尼权力口红410色</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8602,7 +9596,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>安耐晒金钻高效防晒90ml</t>
+          <t>YSL圣罗兰黑金方管13色</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8624,7 +9618,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>雅诗兰黛樱花微精华原生液400ml</t>
+          <t>YSL圣罗兰黑金方管14色</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8646,7 +9640,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>圣罗兰小金条细管口红21号复古正红色</t>
+          <t>YSL圣罗兰黑金方管1968</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8668,7 +9662,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+          <t>YSL圣罗兰银管02色</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8690,7 +9684,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
+          <t>倩碧有油润肤乳125ml</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8712,7 +9706,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>阿玛尼权力口红410色</t>
+          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8734,7 +9728,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管13色</t>
+          <t>SK2大红瓶清爽版80g</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8756,7 +9750,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管14色</t>
+          <t>SK2大红瓶滋润版80g</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8778,7 +9772,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管1968</t>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8800,7 +9794,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>YSL圣罗兰银管02色</t>
+          <t>SK-II 小银瓶精华50ML</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8822,7 +9816,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>倩碧有油润肤乳125ml</t>
+          <t>阿玛尼大师粉底液2号</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8844,7 +9838,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8866,7 +9860,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SK2大红瓶清爽版80g</t>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8888,7 +9882,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润版80g</t>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8910,7 +9904,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8932,7 +9926,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SK-II 小银瓶精华50ML</t>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8954,7 +9948,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>阿玛尼大师粉底液2号</t>
+          <t>GUCCI 香水 茉莉100ML</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8976,7 +9970,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
+          <t>爱马仕李先生的花园淡香水100ml</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8998,7 +9992,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+          <t>爱马仕绯红火参古龙水100ml</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -9020,7 +10014,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -9042,7 +10036,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -9064,7 +10058,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -9086,7 +10080,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>GUCCI 香水 茉莉100ML</t>
+          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -9108,7 +10102,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>李先生的花园(Le Jardin de Monsieur Li)，淡香水，100 ml</t>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -9130,7 +10124,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>绯红火参古龙水（Eau de rhubarbe écarlate）, 古龍水, 100 ml</t>
+          <t>MAC 无暇粉底液NC12 30ML</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -9152,7 +10146,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+          <t>雅诗兰黛 红石榴面霜50ml</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -9174,7 +10168,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -9196,7 +10190,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -9218,7 +10212,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -9240,7 +10234,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MAC妆前保湿精华乳100ML</t>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -9262,7 +10256,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MAC 无暇粉底液NC12 30ML</t>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -9284,7 +10278,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>雅诗兰黛 红石榴面霜50ml</t>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -9306,7 +10300,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>雅诗兰黛 红石榴洁面125ml</t>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -9328,7 +10322,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -9350,7 +10344,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+          <t>兰芝马卡龙隔离30ml紫色</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -9372,7 +10366,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+          <t>兰芝马卡龙隔离30ml绿色</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9394,7 +10388,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9416,7 +10410,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+          <t>NARS蜜粉饼5894 效期24年</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9438,7 +10432,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9460,7 +10454,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9482,7 +10476,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Laneige Skin Veil Base_EX No.40 30ml紫色</t>
+          <t>古驰炼金师花园香草颂香水100ML</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9504,7 +10498,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Laneige Skin Veil Base_EX No.60 30ml绿色</t>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9526,7 +10520,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9548,7 +10542,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>NARS蜜粉饼5894 效期24年</t>
+          <t>YSL新款爱心唇釉610#</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9570,7 +10564,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+          <t>宝格丽白茶淡香150ml</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9592,7 +10586,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SHISEIDO资生堂红腰子精华100ml</t>
+          <t>植村秀绿茶卸妆油150ml</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9614,7 +10608,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>古驰炼金师花园香草颂香水100ML</t>
+          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9636,7 +10630,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>古驰炼金师花园沐光橙香水100ML</t>
+          <t>NARS 水光绚色液体腮红 烟粉豆沙色 BEHAVE 7ml</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9658,7 +10652,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+          <t>Jo Malone祖玛珑英国梨与豌豆花香水30ml</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9680,7 +10674,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>YSL新款爱心唇釉610#</t>
+          <t>兰蔻清爽防晒50ml*2新版</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9702,7 +10696,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>宝格丽白茶淡香150ml</t>
+          <t>古驰炼金师花园狮之心香水100ML</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -9724,7 +10718,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>植村秀绿茶卸妆油150ml</t>
+          <t>古驰炼金师花园桂之舞香水100ML</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9746,7 +10740,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
+          <t>NARS液体腮红 INSATIABLE</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9768,7 +10762,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>NARS 水光绚色液体腮红 烟粉豆沙色 BEHAVE 7ml</t>
+          <t>NARS多功能腮红棒TRANCE 8G</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9790,7 +10784,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Jo Malone祖玛珑英国梨与豌豆花香水30ml</t>
+          <t>NARS多用腮红棒欲焰HOT TAKE 8G</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9812,7 +10806,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>兰蔻清爽防晒双支装50ml*2 新版</t>
+          <t>NARS多用腮红棒爱欲SEX APPEAL 8G</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9834,7 +10828,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>古驰炼金师花园狮之心香水100ML</t>
+          <t>NARS小粉金液体腮红WANDERLUST 7ML</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9856,7 +10850,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>古驰炼金师花园桂之舞香水100ML</t>
+          <t>古驰竹韵浓香75ml</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9878,7 +10872,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>NARS AFTERGLOW LIQUID BLUSH - INSATIABLE</t>
+          <t>欧莱雅紫熨斗30ml 第三代</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9900,7 +10894,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE TRANCE 8G</t>
+          <t>迪奥新版浮雕睡莲洗面奶150ml</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9922,7 +10916,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
+          <t>Clarins娇韵诗焕颜紧致日霜50ml</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9944,7 +10938,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE SEX APPEAL 8G</t>
+          <t>YSL圣罗兰新版恒久无瑕粉底液LN1</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9966,7 +10960,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>NARS AFTER GLOW LIQUID BLUSH -WANDERLUST 7ML</t>
+          <t>兰蔻菁纯臻颜精萃水150ml</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9988,7 +10982,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>古驰竹韵浓香75ml</t>
+          <t>Hermes爱马仕大地淡香对装50m*2</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -10010,7 +11004,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>欧莱雅紫熨斗30ml 第三代</t>
+          <t>MAC魅可 反光镜唇蜜唇釉 228# 棕上镜 AESTHETIC 5ml</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -10026,6 +11020,512 @@
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>
     </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>伊丽莎白雅顿经典润泽护唇膏 SPF15 13g</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>资生堂第四代红腰子精华75ml</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>巴宝莉 粉红恋歌EDT 100ml</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>巴宝莉 情缘男士EDT100ml</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>巴宝莉 我的巴宝莉黑色EDP 90ml</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>CK ONE 100ml(白盒)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>CK ONE 200ml(白盒)</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>CK BE 黑盒香水 100ml</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>CK BE 中性香水200ml黑盒</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>CK 喜欢你男士 50ml</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>CK 喜欢你男士 100ml</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>CK 喜欢你女士100ml</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>CK 自由男士EDT100ml</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿蜜润修护精粹水 300mL</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #669 WARM TEDDY 暖萌泰迪</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>MAC 反光镜唇蜜唇釉 226# 当红镜 CASUAL 5ml</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>MAC魅可 轻尤雾弹 哑光唇釉973 5ml 新版</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>MAC魅可 聚光瓶粉底液 NW11 30ml</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>MAC魅可 轻尤雾弹 哑光子弹头912 3.5ml</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>MAC魅可 聚光瓶粉底液 NC12 30ml</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>GUERLAIN娇兰双管精华50ml</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 Secret Lover 7ml</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>NARS细管哑光唇膏1.5G #136 GET LUCKY 丝绒瑰木</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -6125,7 +6125,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -6807,7 +6807,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -8413,7 +8413,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7553EE46-E7D7-4B43-B96A-222A1C682395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D51AEA-D843-7E4E-9F86-6D326C495990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9100" yWindow="16360" windowWidth="14400" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="449">
   <si>
     <t>序号</t>
   </si>
@@ -58,555 +58,165 @@
     <t>已采集</t>
   </si>
   <si>
-    <t>IVHEGYKJJJVKCIBY</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:05:25</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:06:07</t>
-  </si>
-  <si>
     <t>CPB滋润洁面125ml</t>
   </si>
   <si>
-    <t>2026-05-20 12:06:47</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:07:15</t>
-  </si>
-  <si>
     <t>CPB长管隔离38ml 清爽</t>
   </si>
   <si>
-    <t>待复核</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:07:55</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:08:51</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配</t>
-  </si>
-  <si>
     <t>CPB长管隔离新款37ml滋润</t>
   </si>
   <si>
-    <t>2026-05-20 12:09:31</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:10:31</t>
-  </si>
-  <si>
     <t>MAC 子弹头口红 923# STAY CURIOUS</t>
   </si>
   <si>
-    <t>2026-05-20 12:11:11</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:12:11</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=31.2%)</t>
-  </si>
-  <si>
     <t>MAC热吻棒67</t>
   </si>
   <si>
-    <t>2026-05-20 12:12:51</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:13:21</t>
-  </si>
-  <si>
     <t>MAC紫白饼</t>
   </si>
   <si>
-    <t>2026-05-20 12:14:01</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:14:28</t>
-  </si>
-  <si>
     <t>MiuMiu紅蓋同名女士濃香水50ml</t>
   </si>
   <si>
-    <t>2026-05-20 12:15:08</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:16:58</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=40.0%)</t>
-  </si>
-  <si>
     <t>NARS超方瓶粉底液L4</t>
   </si>
   <si>
-    <t>2026-05-20 12:17:38</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:18:32</t>
-  </si>
-  <si>
     <t>NARS 超方瓶粉底液 L3#</t>
   </si>
   <si>
-    <t>2026-05-20 12:19:12</t>
-  </si>
-  <si>
-    <t>2026-05-20 12:19:46</t>
-  </si>
-  <si>
     <t>NARS 超方瓶粉底液#L1</t>
   </si>
   <si>
-    <t>3B6F6AE7SX2MCMB9</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:02:25</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:03:18</t>
-  </si>
-  <si>
     <t>NARS 粉底液 LO色</t>
   </si>
   <si>
-    <t>2026-05-20 14:03:58</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:04:30</t>
-  </si>
-  <si>
     <t>NARS纳斯定妆散粉</t>
   </si>
   <si>
-    <t>2026-05-20 14:05:10</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:06:15</t>
-  </si>
-  <si>
     <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
   </si>
   <si>
-    <t>2026-05-20 14:06:56</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:08:04</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=27.3%)</t>
-  </si>
-  <si>
     <t>NARS 遮瑕膏 VANILLA色号</t>
   </si>
   <si>
-    <t>2026-05-20 14:08:44</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:09:35</t>
-  </si>
-  <si>
-    <t>nan；品名相似不足(ratio=10.0%)</t>
-  </si>
-  <si>
     <t>NARS5894蜜粉饼10G</t>
   </si>
   <si>
-    <t>2026-05-20 14:10:15</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:11:09</t>
-  </si>
-  <si>
     <t>NARS空气唇釉686 lose control</t>
   </si>
   <si>
-    <t>2026-05-20 14:11:49</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:12:56</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=35.7%)</t>
-  </si>
-  <si>
     <t>NARS空气唇釉thrust</t>
   </si>
   <si>
-    <t>2026-05-20 14:13:36</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:14:20</t>
-  </si>
-  <si>
     <t>NARS细管101 NO ANGEL</t>
   </si>
   <si>
-    <t>2026-05-20 14:15:00</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:15:48</t>
-  </si>
-  <si>
     <t>NARS细管116 START ME UP</t>
   </si>
   <si>
-    <t>2026-05-20 14:16:28</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:17:27</t>
-  </si>
-  <si>
     <t>NARS细管133 TOO HOT TO HOLD</t>
   </si>
   <si>
-    <t>2026-05-20 14:20:01</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:20:47</t>
-  </si>
-  <si>
     <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
   </si>
   <si>
-    <t>2026-05-20 14:21:27</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:22:26</t>
-  </si>
-  <si>
     <t>SK2 神仙水230ml</t>
   </si>
   <si>
-    <t>2026-05-20 14:24:19</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:25:21</t>
-  </si>
-  <si>
     <t>SK2大红瓶滋润面霜100g</t>
   </si>
   <si>
-    <t>2026-05-20 14:26:02</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:26:55</t>
-  </si>
-  <si>
     <t>SK2神仙水330ML</t>
   </si>
   <si>
-    <t>2026-05-20 14:27:35</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:28:41</t>
-  </si>
-  <si>
     <t>SK-II 男士保湿焕活洁面霜120g</t>
   </si>
   <si>
-    <t>2026-05-20 14:29:21</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:30:29</t>
-  </si>
-  <si>
     <t>SK-II 男士焕活护肤精华露 230ml</t>
   </si>
   <si>
-    <t>2026-05-20 14:31:09</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:31:43</t>
-  </si>
-  <si>
-    <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-  </si>
-  <si>
     <t>SK-II 小银瓶淡斑精华露75ml</t>
   </si>
   <si>
-    <t>2026-05-20 14:32:23</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:33:21</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:34:01</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:34:55</t>
-  </si>
-  <si>
     <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
   </si>
   <si>
-    <t>2026-05-20 14:35:35</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:36:35</t>
-  </si>
-  <si>
     <t>TF白麝香 100ml</t>
   </si>
   <si>
-    <t>2026-05-20 14:37:15</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:38:20</t>
-  </si>
-  <si>
     <t>TF黑管哑光16</t>
   </si>
   <si>
-    <t>2026-05-20 14:39:00</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:39:57</t>
-  </si>
-  <si>
     <t>TF黑金唇釉123</t>
   </si>
   <si>
-    <t>2026-05-20 14:41:57</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:42:58</t>
-  </si>
-  <si>
     <t>TF幻魅四色眼影盘#41 Peach Dawn桃色晨曦盘</t>
   </si>
   <si>
-    <t>2026-05-20 14:43:38</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:44:32</t>
-  </si>
-  <si>
     <t>TF幻魅四色眼影盘#GOLDEN MINK</t>
   </si>
   <si>
-    <t>2026-05-20 14:45:13</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:45:39</t>
-  </si>
-  <si>
     <t>TF镜面唇蜜17</t>
   </si>
   <si>
-    <t>2026-05-20 14:46:19</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:47:19</t>
-  </si>
-  <si>
     <t>TF汤姆福特 乌木沉香 100ml</t>
   </si>
   <si>
-    <t>2026-05-20 14:47:59</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:49:01</t>
-  </si>
-  <si>
     <t>TF细黑管52</t>
   </si>
   <si>
-    <t>2026-05-20 14:49:41</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:50:09</t>
-  </si>
-  <si>
-    <t>VAPE未來驅蚊液海藍柑橘噴霧200ml</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:52:08</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:53:37</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=11.1%)</t>
-  </si>
-  <si>
     <t>YSL 细管丝绒纯口红 小黑条 316#</t>
   </si>
   <si>
-    <t>2026-05-20 14:54:17</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:54:43</t>
-  </si>
-  <si>
     <t>YSL黑管唇釉416</t>
   </si>
   <si>
-    <t>2026-05-20 14:55:23</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:56:11</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:56:51</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:57:58</t>
-  </si>
-  <si>
     <t>YSL反转巴黎浓香香水50ml</t>
   </si>
   <si>
-    <t>2026-05-20 14:58:38</t>
-  </si>
-  <si>
-    <t>2026-05-20 14:59:06</t>
-  </si>
-  <si>
     <t>YSL粉气垫替换芯B10</t>
   </si>
   <si>
-    <t>2026-05-20 14:59:46</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:00:39</t>
-  </si>
-  <si>
     <t>YSL粉气垫B10</t>
   </si>
   <si>
-    <t>2026-05-20 15:01:19</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:02:07</t>
-  </si>
-  <si>
     <t>YSL粉气垫替换芯br20</t>
   </si>
   <si>
-    <t>2026-05-20 15:02:47</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:03:27</t>
-  </si>
-  <si>
     <t>YSL黑鸦片浓香50ml</t>
   </si>
   <si>
-    <t>2026-05-20 15:04:07</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:05:14</t>
-  </si>
-  <si>
     <t>YSL口红8B</t>
   </si>
   <si>
-    <t>2026-05-20 15:05:54</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:07:02</t>
-  </si>
-  <si>
     <t>YSL皮革气垫B20替换芯新款</t>
   </si>
   <si>
-    <t>2026-05-20 15:09:03</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:09:59</t>
-  </si>
-  <si>
     <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
   </si>
   <si>
-    <t>2026-05-20 15:10:39</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:12:09</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=30.8%)</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:12:49</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:14:06</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=38.5%)</t>
-  </si>
-  <si>
     <t>YSL细管小金条 #1966</t>
   </si>
   <si>
-    <t>2026-05-20 15:14:46</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:15:41</t>
-  </si>
-  <si>
     <t>YSL自由之水浓香型30ml</t>
   </si>
   <si>
-    <t>2026-05-20 15:16:21</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:17:42</t>
-  </si>
-  <si>
     <t>YSL自由之水浓香50ml</t>
   </si>
   <si>
-    <t>2026-05-20 15:18:22</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:18:52</t>
-  </si>
-  <si>
     <t>YSL自由之水浓香90ml</t>
   </si>
   <si>
-    <t>2026-05-20 15:19:32</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:20:22</t>
-  </si>
-  <si>
     <t>阿玛尼 寄情男士淡香水100ml 新版</t>
   </si>
   <si>
-    <t>2026-05-20 15:21:02</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:22:00</t>
-  </si>
-  <si>
     <t>阿玛尼大师蓝标粉底液1.5</t>
   </si>
   <si>
-    <t>2026-05-20 15:22:40</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:23:32</t>
-  </si>
-  <si>
     <t>阿玛尼红管唇釉206#</t>
   </si>
   <si>
-    <t>2026-05-20 15:24:12</t>
-  </si>
-  <si>
-    <t>2026-05-20 15:25:15</t>
-  </si>
-  <si>
     <t>阿玛尼红管唇釉405-24年</t>
   </si>
   <si>
@@ -640,6 +250,9 @@
     <t>城野医生美白淡斑精华18g</t>
   </si>
   <si>
+    <t>黛珂多重修颜素颜霜35</t>
+  </si>
+  <si>
     <t>黛珂 防晒防水版60g</t>
   </si>
   <si>
@@ -712,6 +325,9 @@
     <t>古驰倾色绒雾唇膏505（金色短管）</t>
   </si>
   <si>
+    <t>未采集</t>
+  </si>
+  <si>
     <t>古驰倾色云雾唇釉505（红色长管）</t>
   </si>
   <si>
@@ -730,183 +346,63 @@
     <t>海蓝之谜精粹水150ml</t>
   </si>
   <si>
-    <t>2026-05-21 09:56:16</t>
-  </si>
-  <si>
-    <t>2026-05-21 09:57:41</t>
-  </si>
-  <si>
     <t>海蓝之谜精华面霜60ml</t>
   </si>
   <si>
-    <t>2026-05-21 09:58:21</t>
-  </si>
-  <si>
-    <t>2026-05-21 09:58:52</t>
-  </si>
-  <si>
     <t>海蓝之谜绿眼霜15ml</t>
   </si>
   <si>
-    <t>2026-05-21 09:59:32</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:00:02</t>
-  </si>
-  <si>
     <t>海蓝之谜面霜100ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:00:42</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:01:09</t>
-  </si>
-  <si>
     <t>海蓝之谜气垫1号</t>
   </si>
   <si>
-    <t>2026-05-21 10:01:49</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:02:37</t>
-  </si>
-  <si>
     <t>赫莲娜 黑绷带50ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:03:17</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:04:18</t>
-  </si>
-  <si>
     <t>赫莲娜黑绷带100ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:04:58</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:05:56</t>
-  </si>
-  <si>
     <t>赫莲娜黑绷带活颜修护舒缓晚霜115ML</t>
   </si>
   <si>
-    <t>2026-05-21 10:06:37</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:07:52</t>
-  </si>
-  <si>
     <t>赫莲娜活颜修护眼霜 15ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:08:32</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:09:33</t>
-  </si>
-  <si>
     <t>赫莲娜绿宝瓶精华 按压款100ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:10:13</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:10:44</t>
-  </si>
-  <si>
     <t>赫莲娜小露珠精粹露200ml新款</t>
   </si>
   <si>
-    <t>2026-05-21 10:12:44</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:13:54</t>
-  </si>
-  <si>
     <t>后拱辰享气韵生水150ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:14:35</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:15:03</t>
-  </si>
-  <si>
     <t>后拱辰享水妍洁面180ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:15:44</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:16:26</t>
-  </si>
-  <si>
     <t>后拱辰享水沄赋活保湿水150ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:17:06</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:17:56</t>
-  </si>
-  <si>
     <t>后拱辰享雪美白水150ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:18:36</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:19:07</t>
-  </si>
-  <si>
     <t>后津率享洁面180ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:19:47</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:20:15</t>
-  </si>
-  <si>
     <t>后津率享平衡水150ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:20:55</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:21:21</t>
-  </si>
-  <si>
     <t>后天气丹PRO水150ML</t>
   </si>
   <si>
-    <t>2026-05-21 10:22:01</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:22:28</t>
-  </si>
-  <si>
     <t>后拱辰享美白洗面奶 180ml</t>
   </si>
   <si>
-    <t>2026-05-21 10:23:08</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:24:15</t>
-  </si>
-  <si>
     <t>纪梵希 粉丝绒N27</t>
   </si>
   <si>
-    <t>2026-05-21 10:24:55</t>
-  </si>
-  <si>
-    <t>2026-05-21 10:25:37</t>
-  </si>
-  <si>
     <t>纪梵希 红丝绒口红#N36</t>
   </si>
   <si>
@@ -982,102 +478,30 @@
     <t>拉夫劳伦地球淡香氛 100ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:42:58</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:43:58</t>
-  </si>
-  <si>
-    <t>nan；品牌不一致；品名相似不足(ratio=66.7%)</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球淡香氛 40ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:44:38</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:45:33</t>
-  </si>
-  <si>
-    <t>nan；品牌不一致；规格不匹配</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 100ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:46:13</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:46:59</t>
-  </si>
-  <si>
-    <t>nan；品牌不一致</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 40ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:47:39</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:48:38</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列淡香氛 摩洛哥橙花 40ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:49:18</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:50:18</t>
-  </si>
-  <si>
-    <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=40.0%)</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 100ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:50:58</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:51:52</t>
-  </si>
-  <si>
-    <t>nan；规格不匹配；品名相似不足(ratio=41.7%)</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 40ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:52:32</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:53:34</t>
-  </si>
-  <si>
-    <t>nan；品牌不一致；规格不匹配；品名相似不足(ratio=16.7%)</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:54:14</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:55:14</t>
-  </si>
-  <si>
     <t>拉夫劳伦地球系列香氛 澳洲檀木 40ml</t>
   </si>
   <si>
-    <t>2026-05-21 11:55:54</t>
-  </si>
-  <si>
-    <t>2026-05-21 11:56:40</t>
-  </si>
-  <si>
     <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
   </si>
   <si>
@@ -1942,24 +1366,14 @@
     <t>NARS细管哑光唇膏1.5G #136 GET LUCKY 丝绒瑰木</t>
   </si>
   <si>
-    <r>
-      <t>黛珂多重修颜素颜霜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.8"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-      </rPr>
-      <t>35</t>
-    </r>
+    <t>VAPE未来驱蚊液 海蓝柑橘喷雾 200ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1973,11 +1387,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12.8"/>
-      <color rgb="FF6AAB73"/>
-      <name val="JetBrains Mono"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2374,40 +1783,16 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2415,25 +1800,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2441,22 +1811,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2464,25 +1822,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2490,22 +1833,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2513,22 +1844,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2536,25 +1855,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2562,25 +1866,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2588,22 +1877,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2611,22 +1888,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2634,22 +1899,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2657,22 +1910,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2680,25 +1921,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2706,1096 +1932,535 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="D17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
-      <c r="D20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
-      <c r="D26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" t="s">
-        <v>94</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" t="s">
-        <v>108</v>
-      </c>
-      <c r="F31" t="s">
-        <v>109</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
       </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>117</v>
-      </c>
-      <c r="F34" t="s">
-        <v>118</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" t="s">
-        <v>120</v>
-      </c>
-      <c r="F35" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
-      <c r="D36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" t="s">
-        <v>123</v>
-      </c>
-      <c r="F36" t="s">
-        <v>124</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
-      <c r="D37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>126</v>
-      </c>
-      <c r="F37" t="s">
-        <v>127</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" t="s">
-        <v>129</v>
-      </c>
-      <c r="F38" t="s">
-        <v>130</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" t="s">
-        <v>132</v>
-      </c>
-      <c r="F39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>448</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" t="s">
-        <v>135</v>
-      </c>
-      <c r="F40" t="s">
-        <v>136</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
-      <c r="D41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" t="s">
-        <v>139</v>
-      </c>
-      <c r="F41" t="s">
-        <v>140</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
-      <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" t="s">
-        <v>142</v>
-      </c>
-      <c r="F42" t="s">
-        <v>143</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
-      <c r="D43" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" t="s">
-        <v>144</v>
-      </c>
-      <c r="F43" t="s">
-        <v>145</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
-      <c r="D44" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" t="s">
-        <v>147</v>
-      </c>
-      <c r="F44" t="s">
-        <v>148</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
-      <c r="D45" t="s">
-        <v>47</v>
-      </c>
-      <c r="E45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" t="s">
-        <v>151</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
       </c>
-      <c r="D46" t="s">
-        <v>47</v>
-      </c>
-      <c r="E46" t="s">
-        <v>153</v>
-      </c>
-      <c r="F46" t="s">
-        <v>154</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
-      <c r="D47" t="s">
-        <v>47</v>
-      </c>
-      <c r="E47" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" t="s">
-        <v>157</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" t="s">
-        <v>159</v>
-      </c>
-      <c r="F48" t="s">
-        <v>160</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
-      <c r="D49" t="s">
-        <v>47</v>
-      </c>
-      <c r="E49" t="s">
-        <v>162</v>
-      </c>
-      <c r="F49" t="s">
-        <v>163</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
       </c>
-      <c r="D50" t="s">
-        <v>47</v>
-      </c>
-      <c r="E50" t="s">
-        <v>165</v>
-      </c>
-      <c r="F50" t="s">
-        <v>166</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" t="s">
-        <v>47</v>
-      </c>
-      <c r="E51" t="s">
-        <v>168</v>
-      </c>
-      <c r="F51" t="s">
-        <v>169</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" t="s">
-        <v>47</v>
-      </c>
-      <c r="E52" t="s">
-        <v>171</v>
-      </c>
-      <c r="F52" t="s">
-        <v>172</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
       </c>
-      <c r="D53" t="s">
-        <v>47</v>
-      </c>
-      <c r="E53" t="s">
-        <v>175</v>
-      </c>
-      <c r="F53" t="s">
-        <v>176</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" t="s">
-        <v>47</v>
-      </c>
-      <c r="E54" t="s">
-        <v>178</v>
-      </c>
-      <c r="F54" t="s">
-        <v>179</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
-      <c r="D55" t="s">
-        <v>47</v>
-      </c>
-      <c r="E55" t="s">
-        <v>181</v>
-      </c>
-      <c r="F55" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>183</v>
+        <v>61</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
       </c>
-      <c r="D56" t="s">
-        <v>47</v>
-      </c>
-      <c r="E56" t="s">
-        <v>184</v>
-      </c>
-      <c r="F56" t="s">
-        <v>185</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>186</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
       </c>
-      <c r="D57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E57" t="s">
-        <v>187</v>
-      </c>
-      <c r="F57" t="s">
-        <v>188</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
       </c>
-      <c r="D58" t="s">
-        <v>47</v>
-      </c>
-      <c r="E58" t="s">
-        <v>190</v>
-      </c>
-      <c r="F58" t="s">
-        <v>191</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
         <v>11</v>
       </c>
-      <c r="D59" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" t="s">
-        <v>193</v>
-      </c>
-      <c r="F59" t="s">
-        <v>194</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>195</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>196</v>
+        <v>66</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>198</v>
+        <v>68</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
@@ -3806,7 +2471,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
@@ -3817,7 +2482,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
@@ -3828,7 +2493,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -3839,7 +2504,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -3850,7 +2515,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -3861,18 +2526,18 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="17">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>640</v>
+        <v>76</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -3883,7 +2548,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -3894,7 +2559,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -3905,7 +2570,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
@@ -3916,7 +2581,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
@@ -3927,7 +2592,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -3938,7 +2603,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
@@ -3949,7 +2614,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -3960,7 +2625,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
@@ -3971,7 +2636,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -3982,7 +2647,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -3993,7 +2658,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -4004,7 +2669,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
@@ -4015,7 +2680,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>218</v>
+        <v>89</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -4026,7 +2691,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>219</v>
+        <v>90</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -4037,7 +2702,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -4048,7 +2713,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -4059,7 +2724,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
@@ -4070,7 +2735,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -4081,7 +2746,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -4092,7 +2757,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -4103,7 +2768,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -4114,7 +2779,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>227</v>
+        <v>98</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
@@ -4125,7 +2790,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -4136,10 +2801,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>229</v>
+        <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4147,605 +2812,362 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>233</v>
+        <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>235</v>
+        <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101" t="s">
-        <v>47</v>
-      </c>
-      <c r="E101" t="s">
-        <v>236</v>
-      </c>
-      <c r="F101" t="s">
-        <v>237</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>11</v>
-      </c>
-      <c r="D102" t="s">
-        <v>47</v>
-      </c>
-      <c r="E102" t="s">
-        <v>239</v>
-      </c>
-      <c r="F102" t="s">
-        <v>240</v>
-      </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>11</v>
-      </c>
-      <c r="D103" t="s">
-        <v>47</v>
-      </c>
-      <c r="E103" t="s">
-        <v>242</v>
-      </c>
-      <c r="F103" t="s">
-        <v>243</v>
-      </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>244</v>
+        <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>11</v>
-      </c>
-      <c r="D104" t="s">
-        <v>47</v>
-      </c>
-      <c r="E104" t="s">
-        <v>245</v>
-      </c>
-      <c r="F104" t="s">
-        <v>246</v>
-      </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="C105" t="s">
-        <v>11</v>
-      </c>
-      <c r="D105" t="s">
-        <v>47</v>
-      </c>
-      <c r="E105" t="s">
-        <v>248</v>
-      </c>
-      <c r="F105" t="s">
-        <v>249</v>
-      </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>250</v>
+        <v>112</v>
       </c>
       <c r="C106" t="s">
-        <v>11</v>
-      </c>
-      <c r="D106" t="s">
-        <v>47</v>
-      </c>
-      <c r="E106" t="s">
-        <v>251</v>
-      </c>
-      <c r="F106" t="s">
-        <v>252</v>
-      </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>11</v>
-      </c>
-      <c r="D107" t="s">
-        <v>47</v>
-      </c>
-      <c r="E107" t="s">
-        <v>254</v>
-      </c>
-      <c r="F107" t="s">
-        <v>255</v>
-      </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>19</v>
-      </c>
-      <c r="D108" t="s">
-        <v>47</v>
-      </c>
-      <c r="E108" t="s">
-        <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>258</v>
-      </c>
-      <c r="G108">
-        <v>0</v>
-      </c>
-      <c r="H108" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>11</v>
-      </c>
-      <c r="D109" t="s">
-        <v>47</v>
-      </c>
-      <c r="E109" t="s">
-        <v>260</v>
-      </c>
-      <c r="F109" t="s">
-        <v>261</v>
-      </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>11</v>
-      </c>
-      <c r="D110" t="s">
-        <v>47</v>
-      </c>
-      <c r="E110" t="s">
-        <v>263</v>
-      </c>
-      <c r="F110" t="s">
-        <v>264</v>
-      </c>
-      <c r="G110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>11</v>
-      </c>
-      <c r="D111" t="s">
-        <v>47</v>
-      </c>
-      <c r="E111" t="s">
-        <v>266</v>
-      </c>
-      <c r="F111" t="s">
-        <v>267</v>
-      </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>268</v>
+        <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
-      </c>
-      <c r="D112" t="s">
-        <v>47</v>
-      </c>
-      <c r="E112" t="s">
-        <v>269</v>
-      </c>
-      <c r="F112" t="s">
-        <v>270</v>
-      </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>271</v>
+        <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" t="s">
-        <v>47</v>
-      </c>
-      <c r="E113" t="s">
-        <v>272</v>
-      </c>
-      <c r="F113" t="s">
-        <v>273</v>
-      </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>274</v>
+        <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" t="s">
-        <v>47</v>
-      </c>
-      <c r="E114" t="s">
-        <v>275</v>
-      </c>
-      <c r="F114" t="s">
-        <v>276</v>
-      </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>277</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" t="s">
-        <v>47</v>
-      </c>
-      <c r="E115" t="s">
-        <v>278</v>
-      </c>
-      <c r="F115" t="s">
-        <v>279</v>
-      </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" t="s">
-        <v>47</v>
-      </c>
-      <c r="E116" t="s">
-        <v>281</v>
-      </c>
-      <c r="F116" t="s">
-        <v>282</v>
-      </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" t="s">
-        <v>47</v>
-      </c>
-      <c r="E117" t="s">
-        <v>284</v>
-      </c>
-      <c r="F117" t="s">
-        <v>285</v>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>286</v>
+        <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>11</v>
-      </c>
-      <c r="D118" t="s">
-        <v>47</v>
-      </c>
-      <c r="E118" t="s">
-        <v>287</v>
-      </c>
-      <c r="F118" t="s">
-        <v>288</v>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>289</v>
+        <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" t="s">
-        <v>47</v>
-      </c>
-      <c r="E119" t="s">
-        <v>290</v>
-      </c>
-      <c r="F119" t="s">
-        <v>291</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>292</v>
+        <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" t="s">
-        <v>47</v>
-      </c>
-      <c r="E120" t="s">
-        <v>293</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>295</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>296</v>
+        <v>128</v>
       </c>
       <c r="C122" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>297</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>298</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>299</v>
+        <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>300</v>
+        <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>301</v>
+        <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>302</v>
+        <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -4753,10 +3175,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>303</v>
+        <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -4764,10 +3186,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>304</v>
+        <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -4775,10 +3197,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="C131" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -4786,10 +3208,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -4797,10 +3219,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -4808,10 +3230,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -4819,10 +3241,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>309</v>
+        <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -4830,10 +3252,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
+        <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -4841,10 +3263,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>311</v>
+        <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -4852,10 +3274,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>312</v>
+        <v>144</v>
       </c>
       <c r="C138" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -4863,10 +3285,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>313</v>
+        <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -4874,10 +3296,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -4885,10 +3307,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>315</v>
+        <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -4896,10 +3318,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>316</v>
+        <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -4907,10 +3329,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>317</v>
+        <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -4918,321 +3340,186 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>19</v>
-      </c>
-      <c r="D145" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" t="s">
-        <v>320</v>
-      </c>
-      <c r="F145" t="s">
-        <v>321</v>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>323</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>19</v>
-      </c>
-      <c r="D146" t="s">
-        <v>12</v>
-      </c>
-      <c r="E146" t="s">
-        <v>324</v>
-      </c>
-      <c r="F146" t="s">
-        <v>325</v>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>327</v>
+        <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>19</v>
-      </c>
-      <c r="D147" t="s">
-        <v>12</v>
-      </c>
-      <c r="E147" t="s">
-        <v>328</v>
-      </c>
-      <c r="F147" t="s">
-        <v>329</v>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>331</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
-      </c>
-      <c r="D148" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" t="s">
-        <v>332</v>
-      </c>
-      <c r="F148" t="s">
-        <v>333</v>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>334</v>
+        <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>19</v>
-      </c>
-      <c r="D149" t="s">
-        <v>12</v>
-      </c>
-      <c r="E149" t="s">
-        <v>335</v>
-      </c>
-      <c r="F149" t="s">
-        <v>336</v>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>338</v>
+        <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>19</v>
-      </c>
-      <c r="D150" t="s">
-        <v>12</v>
-      </c>
-      <c r="E150" t="s">
-        <v>339</v>
-      </c>
-      <c r="F150" t="s">
-        <v>340</v>
-      </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>342</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
-      </c>
-      <c r="D151" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" t="s">
-        <v>343</v>
-      </c>
-      <c r="F151" t="s">
-        <v>344</v>
-      </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>346</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" t="s">
-        <v>12</v>
-      </c>
-      <c r="E152" t="s">
-        <v>347</v>
-      </c>
-      <c r="F152" t="s">
-        <v>348</v>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
       <c r="C153" t="s">
-        <v>19</v>
-      </c>
-      <c r="D153" t="s">
-        <v>12</v>
-      </c>
-      <c r="E153" t="s">
-        <v>350</v>
-      </c>
-      <c r="F153" t="s">
-        <v>351</v>
-      </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>352</v>
+        <v>160</v>
       </c>
       <c r="C154" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>353</v>
+        <v>161</v>
       </c>
       <c r="C155" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>354</v>
+        <v>162</v>
       </c>
       <c r="C156" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>355</v>
+        <v>163</v>
       </c>
       <c r="C157" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="C158" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
       <c r="A159">
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
       <c r="C159" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="C160" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -5240,10 +3527,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>359</v>
+        <v>167</v>
       </c>
       <c r="C161" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -5251,10 +3538,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>360</v>
+        <v>168</v>
       </c>
       <c r="C162" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -5262,10 +3549,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>361</v>
+        <v>169</v>
       </c>
       <c r="C163" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -5273,10 +3560,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>362</v>
+        <v>170</v>
       </c>
       <c r="C164" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -5284,10 +3571,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="C165" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5295,10 +3582,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>364</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -5306,10 +3593,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>365</v>
+        <v>173</v>
       </c>
       <c r="C167" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -5317,10 +3604,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>366</v>
+        <v>174</v>
       </c>
       <c r="C168" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -5328,10 +3615,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>367</v>
+        <v>175</v>
       </c>
       <c r="C169" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -5339,10 +3626,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>368</v>
+        <v>176</v>
       </c>
       <c r="C170" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -5350,10 +3637,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>369</v>
+        <v>177</v>
       </c>
       <c r="C171" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -5361,10 +3648,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>370</v>
+        <v>178</v>
       </c>
       <c r="C172" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -5372,10 +3659,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>371</v>
+        <v>179</v>
       </c>
       <c r="C173" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -5383,10 +3670,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>372</v>
+        <v>180</v>
       </c>
       <c r="C174" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -5394,10 +3681,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>373</v>
+        <v>181</v>
       </c>
       <c r="C175" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -5405,10 +3692,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>374</v>
+        <v>182</v>
       </c>
       <c r="C176" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -5416,10 +3703,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>375</v>
+        <v>183</v>
       </c>
       <c r="C177" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -5427,10 +3714,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>376</v>
+        <v>184</v>
       </c>
       <c r="C178" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -5438,10 +3725,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="C179" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -5449,10 +3736,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>378</v>
+        <v>186</v>
       </c>
       <c r="C180" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -5460,10 +3747,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>379</v>
+        <v>187</v>
       </c>
       <c r="C181" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -5471,10 +3758,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>380</v>
+        <v>188</v>
       </c>
       <c r="C182" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -5482,10 +3769,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>381</v>
+        <v>189</v>
       </c>
       <c r="C183" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -5493,10 +3780,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>382</v>
+        <v>190</v>
       </c>
       <c r="C184" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5504,10 +3791,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>383</v>
+        <v>191</v>
       </c>
       <c r="C185" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -5515,10 +3802,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="C186" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -5526,10 +3813,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>385</v>
+        <v>193</v>
       </c>
       <c r="C187" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -5537,10 +3824,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>386</v>
+        <v>194</v>
       </c>
       <c r="C188" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -5548,10 +3835,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>387</v>
+        <v>195</v>
       </c>
       <c r="C189" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5559,10 +3846,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>388</v>
+        <v>196</v>
       </c>
       <c r="C190" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5570,10 +3857,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>389</v>
+        <v>197</v>
       </c>
       <c r="C191" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -5581,10 +3868,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>390</v>
+        <v>198</v>
       </c>
       <c r="C192" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5592,10 +3879,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>391</v>
+        <v>199</v>
       </c>
       <c r="C193" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -5603,10 +3890,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>392</v>
+        <v>200</v>
       </c>
       <c r="C194" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -5614,10 +3901,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>393</v>
+        <v>201</v>
       </c>
       <c r="C195" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -5625,10 +3912,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>394</v>
+        <v>202</v>
       </c>
       <c r="C196" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -5636,10 +3923,10 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>395</v>
+        <v>203</v>
       </c>
       <c r="C197" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -5647,10 +3934,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>396</v>
+        <v>204</v>
       </c>
       <c r="C198" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -5658,10 +3945,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>397</v>
+        <v>205</v>
       </c>
       <c r="C199" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -5669,10 +3956,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>398</v>
+        <v>206</v>
       </c>
       <c r="C200" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -5680,10 +3967,10 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>399</v>
+        <v>207</v>
       </c>
       <c r="C201" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -5691,10 +3978,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>400</v>
+        <v>208</v>
       </c>
       <c r="C202" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -5702,10 +3989,10 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>401</v>
+        <v>209</v>
       </c>
       <c r="C203" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -5713,10 +4000,10 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>402</v>
+        <v>210</v>
       </c>
       <c r="C204" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -5724,10 +4011,10 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>403</v>
+        <v>211</v>
       </c>
       <c r="C205" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -5735,10 +4022,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>404</v>
+        <v>212</v>
       </c>
       <c r="C206" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -5746,10 +4033,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>405</v>
+        <v>213</v>
       </c>
       <c r="C207" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -5757,10 +4044,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>406</v>
+        <v>214</v>
       </c>
       <c r="C208" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -5768,10 +4055,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>407</v>
+        <v>215</v>
       </c>
       <c r="C209" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -5779,10 +4066,10 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>408</v>
+        <v>216</v>
       </c>
       <c r="C210" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -5790,10 +4077,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>409</v>
+        <v>217</v>
       </c>
       <c r="C211" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -5801,10 +4088,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>410</v>
+        <v>218</v>
       </c>
       <c r="C212" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -5812,10 +4099,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>411</v>
+        <v>219</v>
       </c>
       <c r="C213" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -5823,10 +4110,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>412</v>
+        <v>220</v>
       </c>
       <c r="C214" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -5834,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>413</v>
+        <v>221</v>
       </c>
       <c r="C215" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -5845,10 +4132,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>414</v>
+        <v>222</v>
       </c>
       <c r="C216" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -5856,10 +4143,10 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>415</v>
+        <v>223</v>
       </c>
       <c r="C217" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -5867,10 +4154,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>416</v>
+        <v>224</v>
       </c>
       <c r="C218" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -5878,10 +4165,10 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>417</v>
+        <v>225</v>
       </c>
       <c r="C219" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -5889,10 +4176,10 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>418</v>
+        <v>226</v>
       </c>
       <c r="C220" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -5900,10 +4187,10 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>419</v>
+        <v>227</v>
       </c>
       <c r="C221" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -5911,10 +4198,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>420</v>
+        <v>228</v>
       </c>
       <c r="C222" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -5922,10 +4209,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>421</v>
+        <v>229</v>
       </c>
       <c r="C223" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -5933,10 +4220,10 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="C224" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -5944,10 +4231,10 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>423</v>
+        <v>231</v>
       </c>
       <c r="C225" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -5955,10 +4242,10 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>424</v>
+        <v>232</v>
       </c>
       <c r="C226" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -5966,10 +4253,10 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>425</v>
+        <v>233</v>
       </c>
       <c r="C227" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -5977,10 +4264,10 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>426</v>
+        <v>234</v>
       </c>
       <c r="C228" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -5988,10 +4275,10 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>427</v>
+        <v>235</v>
       </c>
       <c r="C229" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -5999,10 +4286,10 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>428</v>
+        <v>236</v>
       </c>
       <c r="C230" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -6010,10 +4297,10 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>429</v>
+        <v>237</v>
       </c>
       <c r="C231" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -6021,10 +4308,10 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>430</v>
+        <v>238</v>
       </c>
       <c r="C232" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -6032,10 +4319,10 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>431</v>
+        <v>239</v>
       </c>
       <c r="C233" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -6043,10 +4330,10 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>432</v>
+        <v>240</v>
       </c>
       <c r="C234" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -6054,10 +4341,10 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>433</v>
+        <v>241</v>
       </c>
       <c r="C235" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -6065,10 +4352,10 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>434</v>
+        <v>242</v>
       </c>
       <c r="C236" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -6076,10 +4363,10 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>435</v>
+        <v>243</v>
       </c>
       <c r="C237" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -6087,10 +4374,10 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>436</v>
+        <v>244</v>
       </c>
       <c r="C238" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -6098,10 +4385,10 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>437</v>
+        <v>245</v>
       </c>
       <c r="C239" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -6109,10 +4396,10 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>438</v>
+        <v>246</v>
       </c>
       <c r="C240" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -6120,10 +4407,10 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>439</v>
+        <v>247</v>
       </c>
       <c r="C241" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -6131,10 +4418,10 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>440</v>
+        <v>248</v>
       </c>
       <c r="C242" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -6142,10 +4429,10 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>441</v>
+        <v>249</v>
       </c>
       <c r="C243" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -6153,10 +4440,10 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>442</v>
+        <v>250</v>
       </c>
       <c r="C244" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -6164,10 +4451,10 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>443</v>
+        <v>251</v>
       </c>
       <c r="C245" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -6175,10 +4462,10 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>444</v>
+        <v>252</v>
       </c>
       <c r="C246" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -6186,10 +4473,10 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>445</v>
+        <v>253</v>
       </c>
       <c r="C247" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -6197,10 +4484,10 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>446</v>
+        <v>254</v>
       </c>
       <c r="C248" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -6208,10 +4495,10 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>447</v>
+        <v>255</v>
       </c>
       <c r="C249" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -6219,10 +4506,10 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>448</v>
+        <v>256</v>
       </c>
       <c r="C250" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -6230,10 +4517,10 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>449</v>
+        <v>257</v>
       </c>
       <c r="C251" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -6241,10 +4528,10 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="C252" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -6252,10 +4539,10 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>451</v>
+        <v>259</v>
       </c>
       <c r="C253" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -6263,10 +4550,10 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>452</v>
+        <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -6274,10 +4561,10 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>453</v>
+        <v>261</v>
       </c>
       <c r="C255" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -6285,10 +4572,10 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>454</v>
+        <v>262</v>
       </c>
       <c r="C256" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -6296,10 +4583,10 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>455</v>
+        <v>263</v>
       </c>
       <c r="C257" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -6307,10 +4594,10 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>456</v>
+        <v>264</v>
       </c>
       <c r="C258" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -6318,10 +4605,10 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>457</v>
+        <v>265</v>
       </c>
       <c r="C259" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -6329,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>458</v>
+        <v>266</v>
       </c>
       <c r="C260" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -6340,10 +4627,10 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>459</v>
+        <v>267</v>
       </c>
       <c r="C261" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -6351,10 +4638,10 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>460</v>
+        <v>268</v>
       </c>
       <c r="C262" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -6362,10 +4649,10 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>461</v>
+        <v>269</v>
       </c>
       <c r="C263" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -6373,10 +4660,10 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>462</v>
+        <v>270</v>
       </c>
       <c r="C264" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -6384,10 +4671,10 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>463</v>
+        <v>271</v>
       </c>
       <c r="C265" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -6395,10 +4682,10 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>464</v>
+        <v>272</v>
       </c>
       <c r="C266" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -6406,10 +4693,10 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>465</v>
+        <v>273</v>
       </c>
       <c r="C267" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -6417,10 +4704,10 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>466</v>
+        <v>274</v>
       </c>
       <c r="C268" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -6428,10 +4715,10 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>467</v>
+        <v>275</v>
       </c>
       <c r="C269" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -6439,10 +4726,10 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>468</v>
+        <v>276</v>
       </c>
       <c r="C270" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -6450,10 +4737,10 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>469</v>
+        <v>277</v>
       </c>
       <c r="C271" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -6461,10 +4748,10 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>470</v>
+        <v>278</v>
       </c>
       <c r="C272" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -6472,10 +4759,10 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>471</v>
+        <v>279</v>
       </c>
       <c r="C273" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -6483,10 +4770,10 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>472</v>
+        <v>280</v>
       </c>
       <c r="C274" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -6494,10 +4781,10 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>473</v>
+        <v>281</v>
       </c>
       <c r="C275" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -6505,10 +4792,10 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>474</v>
+        <v>282</v>
       </c>
       <c r="C276" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -6516,10 +4803,10 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>475</v>
+        <v>283</v>
       </c>
       <c r="C277" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -6527,10 +4814,10 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>476</v>
+        <v>284</v>
       </c>
       <c r="C278" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -6538,10 +4825,10 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>477</v>
+        <v>285</v>
       </c>
       <c r="C279" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -6549,10 +4836,10 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>478</v>
+        <v>286</v>
       </c>
       <c r="C280" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -6560,10 +4847,10 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>479</v>
+        <v>287</v>
       </c>
       <c r="C281" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -6571,10 +4858,10 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>480</v>
+        <v>288</v>
       </c>
       <c r="C282" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -6582,10 +4869,10 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>480</v>
+        <v>288</v>
       </c>
       <c r="C283" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -6593,10 +4880,10 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>481</v>
+        <v>289</v>
       </c>
       <c r="C284" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -6604,10 +4891,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>482</v>
+        <v>290</v>
       </c>
       <c r="C285" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -6615,10 +4902,10 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>483</v>
+        <v>291</v>
       </c>
       <c r="C286" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -6626,10 +4913,10 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>484</v>
+        <v>292</v>
       </c>
       <c r="C287" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -6637,10 +4924,10 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>485</v>
+        <v>293</v>
       </c>
       <c r="C288" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -6648,10 +4935,10 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>486</v>
+        <v>294</v>
       </c>
       <c r="C289" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -6659,10 +4946,10 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>487</v>
+        <v>295</v>
       </c>
       <c r="C290" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -6670,10 +4957,10 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>488</v>
+        <v>296</v>
       </c>
       <c r="C291" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -6681,10 +4968,10 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>489</v>
+        <v>297</v>
       </c>
       <c r="C292" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -6692,10 +4979,10 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>490</v>
+        <v>298</v>
       </c>
       <c r="C293" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -6703,10 +4990,10 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>491</v>
+        <v>299</v>
       </c>
       <c r="C294" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -6714,10 +5001,10 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>492</v>
+        <v>300</v>
       </c>
       <c r="C295" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -6725,10 +5012,10 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>493</v>
+        <v>301</v>
       </c>
       <c r="C296" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -6736,10 +5023,10 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>494</v>
+        <v>302</v>
       </c>
       <c r="C297" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -6747,10 +5034,10 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>495</v>
+        <v>303</v>
       </c>
       <c r="C298" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -6758,10 +5045,10 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>496</v>
+        <v>304</v>
       </c>
       <c r="C299" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -6769,10 +5056,10 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>497</v>
+        <v>305</v>
       </c>
       <c r="C300" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -6780,10 +5067,10 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>498</v>
+        <v>306</v>
       </c>
       <c r="C301" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -6791,10 +5078,10 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>499</v>
+        <v>307</v>
       </c>
       <c r="C302" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -6802,10 +5089,10 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>500</v>
+        <v>308</v>
       </c>
       <c r="C303" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -6813,10 +5100,10 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>501</v>
+        <v>309</v>
       </c>
       <c r="C304" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -6824,10 +5111,10 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>502</v>
+        <v>310</v>
       </c>
       <c r="C305" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -6835,10 +5122,10 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>503</v>
+        <v>311</v>
       </c>
       <c r="C306" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -6846,10 +5133,10 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>504</v>
+        <v>312</v>
       </c>
       <c r="C307" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -6857,10 +5144,10 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>505</v>
+        <v>313</v>
       </c>
       <c r="C308" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -6868,10 +5155,10 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>506</v>
+        <v>314</v>
       </c>
       <c r="C309" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -6879,10 +5166,10 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>507</v>
+        <v>315</v>
       </c>
       <c r="C310" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -6890,10 +5177,10 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>508</v>
+        <v>316</v>
       </c>
       <c r="C311" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -6901,10 +5188,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>509</v>
+        <v>317</v>
       </c>
       <c r="C312" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -6912,10 +5199,10 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="C313" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -6923,10 +5210,10 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>511</v>
+        <v>319</v>
       </c>
       <c r="C314" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -6934,10 +5221,10 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>512</v>
+        <v>320</v>
       </c>
       <c r="C315" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -6945,10 +5232,10 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>512</v>
+        <v>320</v>
       </c>
       <c r="C316" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -6956,10 +5243,10 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>513</v>
+        <v>321</v>
       </c>
       <c r="C317" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -6967,10 +5254,10 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>514</v>
+        <v>322</v>
       </c>
       <c r="C318" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -6978,10 +5265,10 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>515</v>
+        <v>323</v>
       </c>
       <c r="C319" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -6989,10 +5276,10 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>516</v>
+        <v>324</v>
       </c>
       <c r="C320" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -7000,10 +5287,10 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>517</v>
+        <v>325</v>
       </c>
       <c r="C321" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -7011,10 +5298,10 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>518</v>
+        <v>326</v>
       </c>
       <c r="C322" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -7022,10 +5309,10 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>519</v>
+        <v>327</v>
       </c>
       <c r="C323" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -7033,10 +5320,10 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>520</v>
+        <v>328</v>
       </c>
       <c r="C324" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -7044,10 +5331,10 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>521</v>
+        <v>329</v>
       </c>
       <c r="C325" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -7055,10 +5342,10 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>522</v>
+        <v>330</v>
       </c>
       <c r="C326" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -7066,10 +5353,10 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>523</v>
+        <v>331</v>
       </c>
       <c r="C327" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -7077,10 +5364,10 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>524</v>
+        <v>332</v>
       </c>
       <c r="C328" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -7088,10 +5375,10 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>525</v>
+        <v>333</v>
       </c>
       <c r="C329" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -7099,10 +5386,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>526</v>
+        <v>334</v>
       </c>
       <c r="C330" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -7110,10 +5397,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>527</v>
+        <v>335</v>
       </c>
       <c r="C331" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -7121,10 +5408,10 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>528</v>
+        <v>336</v>
       </c>
       <c r="C332" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -7132,10 +5419,10 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>529</v>
+        <v>337</v>
       </c>
       <c r="C333" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -7143,10 +5430,10 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>530</v>
+        <v>338</v>
       </c>
       <c r="C334" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -7154,10 +5441,10 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>531</v>
+        <v>339</v>
       </c>
       <c r="C335" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -7165,10 +5452,10 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>532</v>
+        <v>340</v>
       </c>
       <c r="C336" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -7176,10 +5463,10 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>533</v>
+        <v>341</v>
       </c>
       <c r="C337" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -7187,10 +5474,10 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>534</v>
+        <v>342</v>
       </c>
       <c r="C338" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -7198,10 +5485,10 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>535</v>
+        <v>343</v>
       </c>
       <c r="C339" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -7209,10 +5496,10 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>536</v>
+        <v>344</v>
       </c>
       <c r="C340" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -7220,10 +5507,10 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>537</v>
+        <v>345</v>
       </c>
       <c r="C341" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -7231,10 +5518,10 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>538</v>
+        <v>346</v>
       </c>
       <c r="C342" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -7242,10 +5529,10 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>539</v>
+        <v>347</v>
       </c>
       <c r="C343" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -7253,10 +5540,10 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>540</v>
+        <v>348</v>
       </c>
       <c r="C344" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -7264,10 +5551,10 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>541</v>
+        <v>349</v>
       </c>
       <c r="C345" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -7275,10 +5562,10 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>542</v>
+        <v>350</v>
       </c>
       <c r="C346" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -7286,10 +5573,10 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>543</v>
+        <v>351</v>
       </c>
       <c r="C347" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -7297,10 +5584,10 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>544</v>
+        <v>352</v>
       </c>
       <c r="C348" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -7308,10 +5595,10 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>545</v>
+        <v>353</v>
       </c>
       <c r="C349" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -7319,10 +5606,10 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>546</v>
+        <v>354</v>
       </c>
       <c r="C350" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -7330,10 +5617,10 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>547</v>
+        <v>355</v>
       </c>
       <c r="C351" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -7341,10 +5628,10 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>548</v>
+        <v>356</v>
       </c>
       <c r="C352" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -7352,10 +5639,10 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>549</v>
+        <v>357</v>
       </c>
       <c r="C353" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -7363,10 +5650,10 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>550</v>
+        <v>358</v>
       </c>
       <c r="C354" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -7374,10 +5661,10 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>551</v>
+        <v>359</v>
       </c>
       <c r="C355" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -7385,10 +5672,10 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>552</v>
+        <v>360</v>
       </c>
       <c r="C356" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -7396,10 +5683,10 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>553</v>
+        <v>361</v>
       </c>
       <c r="C357" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -7407,10 +5694,10 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>554</v>
+        <v>362</v>
       </c>
       <c r="C358" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -7418,10 +5705,10 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>555</v>
+        <v>363</v>
       </c>
       <c r="C359" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -7429,10 +5716,10 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>556</v>
+        <v>364</v>
       </c>
       <c r="C360" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -7440,10 +5727,10 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>557</v>
+        <v>365</v>
       </c>
       <c r="C361" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -7451,10 +5738,10 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>558</v>
+        <v>366</v>
       </c>
       <c r="C362" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -7462,10 +5749,10 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>559</v>
+        <v>367</v>
       </c>
       <c r="C363" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -7473,10 +5760,10 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>560</v>
+        <v>368</v>
       </c>
       <c r="C364" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -7484,10 +5771,10 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>561</v>
+        <v>369</v>
       </c>
       <c r="C365" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -7495,10 +5782,10 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>562</v>
+        <v>370</v>
       </c>
       <c r="C366" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -7506,10 +5793,10 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>563</v>
+        <v>371</v>
       </c>
       <c r="C367" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -7517,10 +5804,10 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>564</v>
+        <v>372</v>
       </c>
       <c r="C368" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -7528,10 +5815,10 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>565</v>
+        <v>373</v>
       </c>
       <c r="C369" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -7539,10 +5826,10 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>566</v>
+        <v>374</v>
       </c>
       <c r="C370" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -7550,10 +5837,10 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>567</v>
+        <v>375</v>
       </c>
       <c r="C371" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -7561,10 +5848,10 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>568</v>
+        <v>376</v>
       </c>
       <c r="C372" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -7572,10 +5859,10 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>569</v>
+        <v>377</v>
       </c>
       <c r="C373" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -7583,10 +5870,10 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>570</v>
+        <v>378</v>
       </c>
       <c r="C374" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -7594,10 +5881,10 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>571</v>
+        <v>379</v>
       </c>
       <c r="C375" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -7605,10 +5892,10 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>572</v>
+        <v>380</v>
       </c>
       <c r="C376" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -7616,10 +5903,10 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>573</v>
+        <v>381</v>
       </c>
       <c r="C377" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -7627,10 +5914,10 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>574</v>
+        <v>382</v>
       </c>
       <c r="C378" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -7638,10 +5925,10 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>575</v>
+        <v>383</v>
       </c>
       <c r="C379" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -7649,10 +5936,10 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>576</v>
+        <v>384</v>
       </c>
       <c r="C380" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -7660,10 +5947,10 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>577</v>
+        <v>385</v>
       </c>
       <c r="C381" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -7671,10 +5958,10 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>578</v>
+        <v>386</v>
       </c>
       <c r="C382" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -7682,10 +5969,10 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>579</v>
+        <v>387</v>
       </c>
       <c r="C383" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -7693,10 +5980,10 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>580</v>
+        <v>388</v>
       </c>
       <c r="C384" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -7704,10 +5991,10 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>581</v>
+        <v>389</v>
       </c>
       <c r="C385" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -7715,10 +6002,10 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>582</v>
+        <v>390</v>
       </c>
       <c r="C386" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -7726,10 +6013,10 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>583</v>
+        <v>391</v>
       </c>
       <c r="C387" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -7737,10 +6024,10 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>584</v>
+        <v>392</v>
       </c>
       <c r="C388" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -7748,10 +6035,10 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>585</v>
+        <v>393</v>
       </c>
       <c r="C389" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -7759,10 +6046,10 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>586</v>
+        <v>394</v>
       </c>
       <c r="C390" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -7770,10 +6057,10 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>587</v>
+        <v>395</v>
       </c>
       <c r="C391" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -7781,10 +6068,10 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>588</v>
+        <v>396</v>
       </c>
       <c r="C392" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -7792,10 +6079,10 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>589</v>
+        <v>397</v>
       </c>
       <c r="C393" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -7803,10 +6090,10 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>590</v>
+        <v>398</v>
       </c>
       <c r="C394" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -7814,10 +6101,10 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>591</v>
+        <v>399</v>
       </c>
       <c r="C395" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -7825,10 +6112,10 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>592</v>
+        <v>400</v>
       </c>
       <c r="C396" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -7836,10 +6123,10 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>593</v>
+        <v>401</v>
       </c>
       <c r="C397" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -7847,10 +6134,10 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>594</v>
+        <v>402</v>
       </c>
       <c r="C398" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -7858,10 +6145,10 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>595</v>
+        <v>403</v>
       </c>
       <c r="C399" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -7869,10 +6156,10 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>596</v>
+        <v>404</v>
       </c>
       <c r="C400" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -7880,10 +6167,10 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>597</v>
+        <v>405</v>
       </c>
       <c r="C401" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -7891,10 +6178,10 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>598</v>
+        <v>406</v>
       </c>
       <c r="C402" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -7902,10 +6189,10 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>599</v>
+        <v>407</v>
       </c>
       <c r="C403" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -7913,10 +6200,10 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>600</v>
+        <v>408</v>
       </c>
       <c r="C404" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -7924,10 +6211,10 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>601</v>
+        <v>409</v>
       </c>
       <c r="C405" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -7935,10 +6222,10 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>602</v>
+        <v>410</v>
       </c>
       <c r="C406" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -7946,10 +6233,10 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>603</v>
+        <v>411</v>
       </c>
       <c r="C407" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -7957,10 +6244,10 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>604</v>
+        <v>412</v>
       </c>
       <c r="C408" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -7968,10 +6255,10 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>605</v>
+        <v>413</v>
       </c>
       <c r="C409" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -7979,10 +6266,10 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>606</v>
+        <v>414</v>
       </c>
       <c r="C410" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -7990,10 +6277,10 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>607</v>
+        <v>415</v>
       </c>
       <c r="C411" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -8001,10 +6288,10 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>608</v>
+        <v>416</v>
       </c>
       <c r="C412" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -8012,10 +6299,10 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>609</v>
+        <v>417</v>
       </c>
       <c r="C413" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -8023,10 +6310,10 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>610</v>
+        <v>418</v>
       </c>
       <c r="C414" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -8034,10 +6321,10 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>611</v>
+        <v>419</v>
       </c>
       <c r="C415" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -8045,10 +6332,10 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>612</v>
+        <v>420</v>
       </c>
       <c r="C416" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -8056,10 +6343,10 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>613</v>
+        <v>421</v>
       </c>
       <c r="C417" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -8067,10 +6354,10 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>614</v>
+        <v>422</v>
       </c>
       <c r="C418" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -8078,10 +6365,10 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>615</v>
+        <v>423</v>
       </c>
       <c r="C419" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -8089,10 +6376,10 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>616</v>
+        <v>424</v>
       </c>
       <c r="C420" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -8100,10 +6387,10 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>617</v>
+        <v>425</v>
       </c>
       <c r="C421" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -8111,10 +6398,10 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>618</v>
+        <v>426</v>
       </c>
       <c r="C422" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -8122,10 +6409,10 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>619</v>
+        <v>427</v>
       </c>
       <c r="C423" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -8133,10 +6420,10 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>620</v>
+        <v>428</v>
       </c>
       <c r="C424" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -8144,10 +6431,10 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>621</v>
+        <v>429</v>
       </c>
       <c r="C425" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -8155,10 +6442,10 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>622</v>
+        <v>430</v>
       </c>
       <c r="C426" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -8166,10 +6453,10 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="C427" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -8177,10 +6464,10 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>624</v>
+        <v>432</v>
       </c>
       <c r="C428" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -8188,10 +6475,10 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>625</v>
+        <v>433</v>
       </c>
       <c r="C429" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -8199,10 +6486,10 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>626</v>
+        <v>434</v>
       </c>
       <c r="C430" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -8210,10 +6497,10 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>627</v>
+        <v>435</v>
       </c>
       <c r="C431" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -8221,10 +6508,10 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>628</v>
+        <v>436</v>
       </c>
       <c r="C432" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -8232,10 +6519,10 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>629</v>
+        <v>437</v>
       </c>
       <c r="C433" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -8243,10 +6530,10 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>630</v>
+        <v>438</v>
       </c>
       <c r="C434" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -8254,10 +6541,10 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>631</v>
+        <v>439</v>
       </c>
       <c r="C435" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -8265,10 +6552,10 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>632</v>
+        <v>440</v>
       </c>
       <c r="C436" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -8276,10 +6563,10 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>633</v>
+        <v>441</v>
       </c>
       <c r="C437" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -8287,10 +6574,10 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>634</v>
+        <v>442</v>
       </c>
       <c r="C438" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -8298,10 +6585,10 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>635</v>
+        <v>443</v>
       </c>
       <c r="C439" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -8309,10 +6596,10 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>636</v>
+        <v>444</v>
       </c>
       <c r="C440" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -8320,10 +6607,10 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>637</v>
+        <v>445</v>
       </c>
       <c r="C441" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -8331,10 +6618,10 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>638</v>
+        <v>446</v>
       </c>
       <c r="C442" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -8342,14 +6629,14 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>639</v>
+        <v>447</v>
       </c>
       <c r="C443" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -7751,7 +7751,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J444"/>
+  <dimension ref="A1:J445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -7284,12 +7284,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+          <t>赫莲娜 绿宝瓶新肌水400ml</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -7306,12 +7306,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+          <t>赫莲娜 绿宝瓶新肌水200ml</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -10226,6 +10226,28 @@
       <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr"/>
     </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>443</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>资生堂 小针管眼霜（新款）20mL</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K447"/>
+  <dimension ref="A1:K450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,7 +813,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+          <t>NARS超绒瓶粉底液45ml #L3 GOBI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -828,7 +828,11 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1112,7 +1116,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK-II 男士焕活护肤精华露 230ml</t>
+          <t>SK2男士神仙水230ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1645,7 +1649,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YSL皮革气垫正装B20新款</t>
+          <t>YSL皮革气垫B20新款</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3176,7 +3180,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3199,7 +3203,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3222,7 +3226,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3245,7 +3249,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3268,7 +3272,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3314,7 +3318,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3360,7 +3364,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3383,7 +3387,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -3429,7 +3433,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -3452,7 +3456,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3475,7 +3479,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -3498,7 +3502,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3544,7 +3548,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3567,7 +3571,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3590,7 +3594,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3613,7 +3617,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -3659,7 +3663,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3682,7 +3686,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -3728,7 +3732,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3774,7 +3778,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3797,7 +3801,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3820,7 +3824,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3843,7 +3847,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3866,7 +3870,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -3889,7 +3893,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -3912,7 +3916,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -3935,7 +3939,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -3958,7 +3962,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -3981,7 +3985,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -4004,7 +4008,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4027,7 +4031,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4050,7 +4054,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4073,7 +4077,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4119,7 +4123,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4142,7 +4146,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4165,7 +4169,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4211,7 +4215,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4234,7 +4238,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4257,7 +4261,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4280,7 +4284,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -4303,7 +4307,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -4326,7 +4330,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -4349,7 +4353,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4372,7 +4376,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4395,7 +4399,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -4418,7 +4422,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -4441,7 +4445,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -4464,7 +4468,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4487,7 +4491,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -4510,7 +4514,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4533,7 +4537,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4556,7 +4560,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4579,7 +4583,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4602,7 +4606,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4625,7 +4629,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4648,7 +4652,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -4671,7 +4675,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -4694,7 +4698,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -4717,7 +4721,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4740,7 +4744,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -4763,7 +4767,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -4786,7 +4790,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4832,7 +4836,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -4855,7 +4859,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -4882,7 +4886,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -4905,7 +4909,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -4928,7 +4932,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4951,7 +4955,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -4974,7 +4978,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -4997,7 +5001,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -5020,7 +5024,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -5043,7 +5047,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -5066,7 +5070,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -5089,7 +5093,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -5112,7 +5116,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -5135,7 +5139,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -5158,7 +5162,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -5181,7 +5185,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -5204,7 +5208,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5227,7 +5231,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5250,7 +5254,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5273,7 +5277,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -5296,7 +5300,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -5319,7 +5323,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5342,7 +5346,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5365,7 +5369,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5388,7 +5392,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5411,7 +5415,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5434,7 +5438,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5457,7 +5461,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5480,7 +5484,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5503,7 +5507,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5526,7 +5530,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5549,7 +5553,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -5572,7 +5576,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -5595,7 +5599,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -5618,7 +5622,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -5641,7 +5645,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -5664,7 +5668,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -5710,7 +5714,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -5733,7 +5737,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -5756,7 +5760,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -5779,7 +5783,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -5802,7 +5806,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -5825,7 +5829,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -5848,7 +5852,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -5871,7 +5875,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -5894,7 +5898,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -5917,7 +5921,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -5940,7 +5944,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -5963,7 +5967,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -5986,7 +5990,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6009,7 +6013,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6032,7 +6036,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6055,7 +6059,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6078,7 +6082,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6101,7 +6105,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -6124,7 +6128,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -6147,7 +6151,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -6170,7 +6174,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -6193,7 +6197,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -6216,7 +6220,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -6239,7 +6243,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -6262,7 +6266,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -6285,7 +6289,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -6308,7 +6312,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -6331,7 +6335,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -6354,7 +6358,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6400,7 +6404,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -6423,7 +6427,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -6446,7 +6450,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -6469,7 +6473,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -6515,7 +6519,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -6538,7 +6542,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6561,7 +6565,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -6607,7 +6611,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -6630,7 +6634,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -6653,7 +6657,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -6676,7 +6680,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -6694,12 +6698,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>圣罗兰黑色皮革气垫替换装B10</t>
+          <t>ysl黑气垫替换芯B10</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -6709,7 +6713,11 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6722,7 +6730,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -6745,7 +6753,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -6768,7 +6776,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -6791,7 +6799,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -6814,7 +6822,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -6860,7 +6868,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -6883,7 +6891,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -6906,7 +6914,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -6929,7 +6937,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -6952,7 +6960,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -6975,7 +6983,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -6998,7 +7006,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -7021,7 +7029,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -7044,7 +7052,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7067,7 +7075,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7090,7 +7098,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -7113,7 +7121,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7136,7 +7144,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7159,7 +7167,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7182,7 +7190,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7205,7 +7213,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7228,7 +7236,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7251,7 +7259,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -7274,7 +7282,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -7297,7 +7305,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7320,7 +7328,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7343,7 +7351,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7366,7 +7374,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7389,7 +7397,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7412,7 +7420,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7435,7 +7443,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7458,7 +7466,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7481,7 +7489,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -7504,7 +7512,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -7527,7 +7535,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -7550,7 +7558,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -7573,7 +7581,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -7596,7 +7604,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -7619,7 +7627,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -7642,7 +7650,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -7665,7 +7673,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -7688,7 +7696,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -7711,7 +7719,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -7734,7 +7742,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -7757,7 +7765,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -7780,7 +7788,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -7803,7 +7811,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -7826,7 +7834,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -7849,7 +7857,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -7872,7 +7880,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -7895,7 +7903,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -7918,7 +7926,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -7941,7 +7949,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -7964,7 +7972,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -7987,7 +7995,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -8010,7 +8018,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -8033,7 +8041,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -8056,7 +8064,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -8079,7 +8087,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -8102,7 +8110,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -8125,7 +8133,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -8148,7 +8156,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -8171,7 +8179,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -8194,7 +8202,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -8217,7 +8225,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -8240,7 +8248,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -8263,7 +8271,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -8286,7 +8294,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -8309,7 +8317,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -8332,7 +8340,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -8355,7 +8363,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -8378,7 +8386,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -8401,7 +8409,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -8424,7 +8432,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -8447,7 +8455,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -8470,7 +8478,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -8493,7 +8501,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -8516,7 +8524,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -8539,7 +8547,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -8562,7 +8570,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -8585,7 +8593,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -8608,7 +8616,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -8631,7 +8639,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -8654,7 +8662,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -8677,7 +8685,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -8700,7 +8708,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -8723,7 +8731,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -8746,7 +8754,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -8769,7 +8777,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -8792,7 +8800,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -8815,7 +8823,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -8838,7 +8846,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -8861,7 +8869,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -8884,7 +8892,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -8907,7 +8915,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -8930,7 +8938,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -8953,7 +8961,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -8976,7 +8984,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -8999,7 +9007,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -9022,7 +9030,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -9045,7 +9053,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -9068,7 +9076,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -9091,7 +9099,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -9114,7 +9122,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -9137,7 +9145,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -9160,7 +9168,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -9183,7 +9191,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -9206,7 +9214,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -9229,7 +9237,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9252,7 +9260,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9275,7 +9283,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9298,7 +9306,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9321,7 +9329,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -9344,7 +9352,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -9367,7 +9375,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -9390,7 +9398,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -9413,7 +9421,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -9436,7 +9444,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -9459,7 +9467,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -9482,7 +9490,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -9505,7 +9513,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -9528,7 +9536,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -9551,7 +9559,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -9574,7 +9582,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -9597,7 +9605,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -9620,7 +9628,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -9643,7 +9651,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -9666,7 +9674,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -9689,7 +9697,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -9712,7 +9720,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -9735,7 +9743,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -9758,7 +9766,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -9781,7 +9789,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -9804,7 +9812,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -9827,7 +9835,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -9850,7 +9858,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -9873,7 +9881,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -9896,7 +9904,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -9919,7 +9927,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -9946,7 +9954,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -9973,7 +9981,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -9996,7 +10004,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -10019,7 +10027,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -10042,7 +10050,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -10065,7 +10073,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -10088,7 +10096,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -10111,7 +10119,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10134,7 +10142,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -10157,7 +10165,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -10180,7 +10188,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -10203,7 +10211,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -10226,7 +10234,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -10249,7 +10257,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -10272,7 +10280,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -10295,7 +10303,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -10318,7 +10326,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -10341,7 +10349,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -10364,7 +10372,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -10387,7 +10395,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -10410,7 +10418,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -10433,7 +10441,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -10456,7 +10464,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -10479,7 +10487,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -10502,7 +10510,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -10525,7 +10533,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -10548,7 +10556,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -10571,7 +10579,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -10594,7 +10602,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -10617,7 +10625,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -10640,7 +10648,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -10663,7 +10671,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -10686,7 +10694,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -10709,7 +10717,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -10732,7 +10740,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -10755,7 +10763,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
@@ -10767,6 +10775,75 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr"/>
     </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>资生堂盼丽风姿滋润面霜50ml新</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>资生堂红腰子面霜50ml新</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 黑绷带活颜修护晚霜100ml（50%玻色因）</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/搜索名单.xlsx
+++ b/搜索名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+          <t>MiuMiu红盖同名女士浓香水50ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,7 +667,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3819,7 +3823,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球淡香氛 100ml</t>
+          <t>欧珑无极乌龙护手霜30ML</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3842,7 +3846,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球淡香氛 40ml</t>
+          <t>莱珀妮反重力精华50ml</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3865,7 +3869,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 100ml</t>
+          <t>兰蔻 持妆粉底液 PO-01 30ml</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3888,7 +3892,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 40ml</t>
+          <t xml:space="preserve">兰蔻 极光乳液净澈焕肤亮白乳液 75ml </t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3911,7 +3915,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 摩洛哥橙花 40ml</t>
+          <t>兰蔻 极光水250ML新款</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3934,7 +3938,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 100ml</t>
+          <t>兰蔻二代精华肌底液115ml</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3957,7 +3961,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列淡香氛 普罗旺斯鼠尾草 40ml</t>
+          <t>兰蔻粉水400ml 旧版</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3980,7 +3984,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
+          <t>兰蔻粉水400ml 新版</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4003,7 +4007,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 40ml</t>
+          <t>兰蔻第二代肌底液100ml</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4026,7 +4030,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+          <t>兰蔻极光洁面乳125ml</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4049,7 +4053,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 30ML</t>
+          <t>兰蔻极光美白精华50ml 新款</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4072,7 +4076,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>欧珑无极乌龙护手霜30ML</t>
+          <t>兰蔻菁纯丝绒雾面唇膏200#</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4095,7 +4099,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>莱珀妮反重力精华50ml</t>
+          <t>兰蔻奇迹香水30ml</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4118,7 +4122,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>兰蔻 持妆粉底液 PO-01 30ml</t>
+          <t>兰蔻清爽防晒50ml 25款</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4141,7 +4145,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">兰蔻 极光乳液净澈焕肤亮白乳液 75ml </t>
+          <t>兰蔻是我淡香水 50ml</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4164,7 +4168,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>兰蔻 极光水250ML新款</t>
+          <t>兰蔻小白管防晒乳50ml</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4187,7 +4191,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>兰蔻二代精华肌底液115ml</t>
+          <t>兰蔻小黑瓶肌底液第二代100ml*2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4210,7 +4214,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>兰蔻粉水400ml 旧版</t>
+          <t>兰蔻小黑瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4233,7 +4237,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>兰蔻粉水400ml 新版</t>
+          <t>兰蔻小蛮腰哑光296唇膏</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4256,7 +4260,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>兰蔻第二代肌底液100ml</t>
+          <t>罗拉散粉经典款29G</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4279,7 +4283,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>兰蔻极光洁面乳125ml</t>
+          <t>马丁马吉拉-慵懒周末100ml</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4302,7 +4306,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>兰蔻极光美白精华50ml 新款</t>
+          <t>慕拉得塑颜修复A醇精华30ml</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4325,7 +4329,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>兰蔻菁纯丝绒雾面唇膏200#</t>
+          <t>欧珑赤霞橘光护手霜30ML</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4348,7 +4352,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>兰蔻奇迹香水30ml</t>
+          <t>欧珑淡香精  赤霞橘光 100ML</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4371,7 +4375,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>兰蔻清爽防晒50ml 25款</t>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4394,7 +4398,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>兰蔻是我淡香水 50ml</t>
+          <t>欧珑淡香精 赤霞橘光 30ML</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4417,7 +4421,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>兰蔻小白管防晒乳50ml</t>
+          <t>欧珑淡香精 情柚独钟 30ML</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4440,7 +4444,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>兰蔻小黑瓶肌底液第二代100ml*2</t>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4463,7 +4467,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>兰蔻小黑瓶眼霜15ml</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4486,7 +4490,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>兰蔻小蛮腰哑光296唇膏</t>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4509,7 +4513,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>倩碧 紫胖子卸妆膏125ml</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4532,7 +4536,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>马丁马吉拉-慵懒周末100ml</t>
+          <t xml:space="preserve">倩碧小雏菊裸色阳光腮#05 </t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4555,7 +4559,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>薇迪薇奇净颜美肌洁面乳</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4578,7 +4582,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
+          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4601,7 +4605,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>欧珑淡香精  赤霞橘光 100ML</t>
+          <t>伟博金萃高纯度鱼油1100毫克Omega-3 60粒</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4616,7 +4620,11 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4624,7 +4632,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4647,7 +4655,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>欧珑淡香精 赤霞橘光 30ML</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4670,7 +4678,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4693,7 +4701,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4716,7 +4724,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>雅诗兰黛DW  2c0</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4739,7 +4747,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4762,7 +4770,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>倩碧 紫胖子卸妆膏125ml</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4785,7 +4793,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">倩碧小雏菊裸色阳光腮#05 </t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4808,7 +4816,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4831,7 +4839,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4854,7 +4862,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100毫克Omega-3 60粒</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4869,11 +4877,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4881,7 +4885,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>茵芙纱 三色遮瑕4.5g</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>资生堂安耐晒60ml新版</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4927,7 +4931,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>资生堂百优面霜 75ml</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4950,7 +4954,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>资生堂蓝胖子150ml 新版</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4973,7 +4977,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
+          <t>资生堂蓝胖子防晒50ml</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4996,7 +5000,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>资生堂蓝胖子防晒50ml（新版）</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5019,7 +5023,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂琉璃洁面125ml</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5042,7 +5046,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+          <t>资生堂琉璃洁面50ml新版</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5065,7 +5069,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>雅诗兰黛线雕精华50ml（新版）</t>
+          <t>资生堂琉璃爽肤水74ml新版</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5088,7 +5092,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+          <t>资生堂男生爽肤水150ml</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5111,7 +5115,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>雅诗兰黛智妍晚霜75ml</t>
+          <t>资生堂男士洁面乳125ml</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5134,7 +5138,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>茵芙纱 三色遮瑕4.5g</t>
+          <t>资生堂男士乳液100ml</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5157,7 +5161,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>资生堂安耐晒60ml新版</t>
+          <t>资生堂悦微清爽水150ml（新版）</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5180,7 +5184,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>资生堂百优面霜 75ml</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5203,7 +5207,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子150ml 新版</t>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5226,7 +5230,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子防晒50ml</t>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5249,7 +5253,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子防晒50ml（新版）</t>
+          <t>资生堂悦薇清爽乳100ml（新版）</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5272,7 +5276,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>资生堂琉璃洁面125ml</t>
+          <t>祖玛珑 蓝风铃香水100ml</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5295,7 +5299,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>资生堂琉璃洁面50ml新版</t>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5318,7 +5322,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>资生堂琉璃爽肤水74ml新版</t>
+          <t>阿玛尼大师蓝标粉底液2#</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5341,7 +5345,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>资生堂男生爽肤水150ml</t>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5364,7 +5368,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>资生堂男士洁面乳125ml</t>
+          <t>阿玛尼权力PR0粉底30ml#3</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5387,7 +5391,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>资生堂男士乳液100ml</t>
+          <t>阿玛尼「大师」锁光粉底液#3</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5410,7 +5414,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>资生堂悦微清爽水150ml（新版）</t>
+          <t>阿玛尼气垫替换芯3号</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5433,7 +5437,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
+          <t>兰蔻水唇釉275#</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5456,7 +5460,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>资生堂悦薇纯A小针管眼霜20ml</t>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5479,7 +5483,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>资生堂悦薇滋润乳100ml（新版）</t>
+          <t>POLA 黑BA洁面</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5502,7 +5506,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>资生堂悦薇清爽乳100ml（新版）</t>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5525,7 +5529,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>祖玛珑 蓝风铃香水100ml</t>
+          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5548,7 +5552,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5571,7 +5575,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>阿玛尼大师蓝标粉底液2#</t>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底30ml#2</t>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底30ml#3</t>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5640,7 +5644,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>阿玛尼「大师」锁光粉底液#3</t>
+          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5663,7 +5667,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>阿玛尼气垫替换芯3号</t>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5686,7 +5690,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>兰蔻水唇釉275#</t>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>古驰绮梦栀子花香水50ml浓香型</t>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5732,7 +5736,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>POLA 黑BA洁面</t>
+          <t>SK2大红瓶面霜80g滋润</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5755,7 +5759,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
+          <t>雅诗兰黛红石榴洁面125ml</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5801,7 +5805,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5824,7 +5828,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5847,7 +5851,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5870,7 +5874,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5893,7 +5897,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5916,7 +5920,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5939,7 +5943,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5962,7 +5966,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>植村秀持久保湿定妆喷雾100ml</t>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5985,7 +5989,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SK2大红瓶面霜80g滋润</t>
+          <t>CK Man男士香水 50ml EDT</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6008,7 +6012,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6031,7 +6035,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面125ml</t>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6054,7 +6058,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6077,7 +6081,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6100,7 +6104,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
+          <t>娇韵诗 双萃眼霜 20ml</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6123,7 +6127,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6146,7 +6150,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO百优面霜50ml</t>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6169,7 +6173,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+          <t>娇韵诗 抚纹油 100ml</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6192,7 +6196,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6215,7 +6219,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+          <t>欧舒丹樱花护手霜三支装</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6238,7 +6242,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CK Man男士香水 50ml EDT</t>
+          <t>欧舒丹乳木果身体乳250ml</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -6261,7 +6265,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+          <t>欧舒丹玫瑰身体乳250ml</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6284,7 +6288,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+          <t>海蓝之谜洁面125ml</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6307,7 +6311,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+          <t>CPB滋润洗面奶125ml</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6330,7 +6334,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>古驰 竹韵女士香水浓香型50ml</t>
+          <t>CPB美白短管隔离30ml</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6353,7 +6357,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>娇韵诗 双萃眼霜 20ml</t>
+          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6376,7 +6380,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>娇韵诗 双萃新版第9代 75ml</t>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6399,7 +6403,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+          <t>圣罗兰爱心黑管唇釉620</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6422,7 +6426,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>娇韵诗 抚纹油 100ml</t>
+          <t>圣罗兰黑色皮革气垫B10</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6445,7 +6449,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>娇韵诗 双萃新版第9代 30ml</t>
+          <t>ysl黑气垫替换芯B10</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6460,7 +6464,11 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -6468,7 +6476,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>欧舒丹樱花护手霜三支装</t>
+          <t>兰蔻菁纯粉底液100</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6491,7 +6499,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>欧舒丹乳木果身体乳250ml</t>
+          <t>SK2骨胶原乳液100g</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6514,7 +6522,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>欧舒丹玫瑰身体乳250ml</t>
+          <t>SK2清莹露230ml</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6537,7 +6545,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>海蓝之谜洁面125ml</t>
+          <t>SK2立体修护眼霜15g两瓶装</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6560,7 +6568,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CPB滋润洗面奶125ml</t>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6583,7 +6591,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CPB美白短管隔离30ml</t>
+          <t>碧欧泉男士水动力乳液100ml</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6606,7 +6614,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6629,7 +6637,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+          <t>圣罗兰女神逆龄粉底液B20</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6652,7 +6660,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉620</t>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6675,7 +6683,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>圣罗兰黑色皮革气垫B10</t>
+          <t>兰蔻第三代肌底液100ml</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6698,7 +6706,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>ysl黑气垫替换芯B10</t>
+          <t>衰败城市牛郎眼影</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6713,11 +6721,7 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6725,7 +6729,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>兰蔻菁纯粉底液100</t>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6748,7 +6752,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SK2骨胶原乳液100g</t>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6771,7 +6775,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SK2清莹露230ml</t>
+          <t>爱马仕大地淡香水50ml</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6794,7 +6798,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SK2立体修护眼霜15g两瓶装</t>
+          <t>苏秘气垫1号</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6817,7 +6821,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6840,7 +6844,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>碧欧泉男士水动力乳液100ml</t>
+          <t>YSL圣罗兰夜皇后50ml</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6863,7 +6867,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6886,7 +6890,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>圣罗兰女神逆龄粉底液B20</t>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6909,7 +6913,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6932,7 +6936,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>兰蔻第三代肌底液100ml</t>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6955,7 +6959,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>衰败城市牛郎眼影</t>
+          <t>资生堂蓝胖子防晒50ml对装</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6978,7 +6982,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+          <t xml:space="preserve">阿玛尼权力PR0粉底1.5 30ml </t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -7001,7 +7005,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+          <t>兰蔻小黑瓶眼霜20ml</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -7024,7 +7028,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>爱马仕大地淡香水50ml</t>
+          <t>HR赫莲娜绿眼霜对装</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -7047,7 +7051,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>苏秘气垫1号</t>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -7070,7 +7074,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
+          <t>MAC无瑕粉底液N11 2.0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7093,7 +7097,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>YSL圣罗兰夜皇后50ml</t>
+          <t>MAC无瑕粉底液N18 2.0</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7116,7 +7120,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+          <t>MAC无瑕粉底液NC11 2.0</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7139,7 +7143,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7162,7 +7166,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
+          <t>黛珂牛油果乳液300ml*2</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7185,7 +7189,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7208,7 +7212,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>资生堂蓝胖子防晒50ml对装</t>
+          <t>GUCCI绮梦馥栀100ML</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7231,7 +7235,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">阿玛尼权力PR0粉底1.5 30ml </t>
+          <t>GUCCI花悦绽放100ML浓香</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -7254,7 +7258,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>兰蔻小黑瓶眼霜20ml</t>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7277,7 +7281,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿眼霜对装</t>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7300,7 +7304,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
+          <t>GUCCI绮梦香草兰香100ml</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7323,7 +7327,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N11 2.0</t>
+          <t>GUCCI绮梦香草兰香50ml</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7346,7 +7350,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N18 2.0</t>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7369,7 +7373,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
+          <t>赫莲娜 绿宝瓶新肌水400ml</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7392,7 +7396,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
+          <t>赫莲娜 绿宝瓶新肌水200ml</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7415,7 +7419,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液300ml*2</t>
+          <t>SK-II光子小灯泡精华露50ml</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7438,7 +7442,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
+          <t>SK-II晶致美肤乳液100g</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7461,7 +7465,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
+          <t>SKII女士洗面奶120g/支</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7484,7 +7488,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
+          <t>SK-II前男友面膜10片装</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7507,7 +7511,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
+          <t>SK-II前男友面膜10片装</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7530,7 +7534,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
+          <t>SKII大红瓶面霜80g清爽</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7553,7 +7557,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7576,7 +7580,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香50ml</t>
+          <t>后Whoo天气丹PRO乳110ML</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7599,7 +7603,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7622,7 +7626,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>赫莲娜 绿宝瓶新肌水400ml</t>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7645,7 +7649,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>赫莲娜 绿宝瓶新肌水200ml</t>
+          <t>SK-II小灯泡新版50ml</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7668,7 +7672,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SK-II光子小灯泡精华露50ml</t>
+          <t>SKII光子小灯泡75ml</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7691,7 +7695,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SK-II晶致美肤乳液100g</t>
+          <t>SKII洁面油250ml</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7714,7 +7718,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SKII女士洗面奶120g/支</t>
+          <t>纪梵希粉丝绒N37</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7737,7 +7741,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
+          <t>圣罗兰爱心黑管唇釉440</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7760,7 +7764,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7783,7 +7787,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g清爽</t>
+          <t>雅诗兰黛红石榴水200ml两支装</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7806,7 +7810,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>NARS空气唇釉GIPSY吉普赛</t>
+          <t>SK2小银瓶50ml两瓶装</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7829,7 +7833,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>后Whoo天气丹PRO乳110ML</t>
+          <t>SK2大红瓶滋润面霜50g</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7852,7 +7856,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+          <t>馥蕾诗西柚香皂</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7875,7 +7879,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7898,7 +7902,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>SK-II小灯泡新版50ml</t>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7921,7 +7925,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>SKII光子小灯泡75ml</t>
+          <t>馥蕾诗睡莲日霜50ml</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7944,7 +7948,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7967,7 +7971,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>纪梵希粉丝绒N37</t>
+          <t>馥蕾诗小苍兰香皂</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7990,7 +7994,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉440</t>
+          <t>雅诗兰黛白金粉底液1W0</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -8013,7 +8017,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+          <t>馥蕾诗红茶精粹水250ml</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -8036,7 +8040,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴水200ml两支装</t>
+          <t>雅诗兰黛白金粉底液1CO</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -8059,7 +8063,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>SK2小银瓶50ml两瓶装</t>
+          <t>娇韵诗美白滋润水200ml</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -8082,7 +8086,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润面霜50g</t>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -8105,7 +8109,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>馥蕾诗西柚香皂</t>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8128,7 +8132,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>馥蕾诗玫瑰花瓣水400ml</t>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -8151,7 +8155,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>馥蕾诗红茶紧致面霜50ml</t>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8174,7 +8178,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>馥蕾诗睡莲日霜50ml</t>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -8197,7 +8201,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+          <t>科颜氏男士乳液125ml</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -8220,7 +8224,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>馥蕾诗小苍兰香皂</t>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -8243,7 +8247,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>雅诗兰黛白金粉底液1W0</t>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -8266,7 +8270,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>馥蕾诗红茶精粹水250ml</t>
+          <t>资生堂安耐晒90ml</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -8289,7 +8293,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>雅诗兰黛白金粉底液1CO</t>
+          <t>安耐晒金钻高效防晒90ml</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -8312,7 +8316,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>娇韵诗美白滋润水200ml</t>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -8335,7 +8339,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>娇韵诗焕颜紧致晚霜50ml</t>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -8358,7 +8362,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -8381,7 +8385,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -8404,7 +8408,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+          <t>阿玛尼权力口红410色</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8427,7 +8431,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+          <t>YSL圣罗兰黑金方管13色</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8450,7 +8454,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>科颜氏男士乳液125ml</t>
+          <t>YSL圣罗兰黑金方管14色</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8473,7 +8477,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+          <t>YSL圣罗兰黑金方管1968</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8496,7 +8500,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+          <t>YSL圣罗兰银管02色</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8519,7 +8523,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>资生堂安耐晒90ml</t>
+          <t>倩碧有油润肤乳125ml</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8542,7 +8546,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>安耐晒金钻高效防晒90ml</t>
+          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8565,7 +8569,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>雅诗兰黛樱花微精华原生液400ml</t>
+          <t>SK2大红瓶清爽版80g</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8588,7 +8592,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>圣罗兰小金条细管口红21号复古正红色</t>
+          <t>SK2大红瓶滋润版80g</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8611,7 +8615,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8634,7 +8638,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
+          <t>SK-II 小银瓶精华50ML</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8657,7 +8661,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>阿玛尼权力口红410色</t>
+          <t>阿玛尼大师粉底液2号</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8680,7 +8684,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管13色</t>
+          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8703,7 +8707,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管14色</t>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8726,7 +8730,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管1968</t>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8749,7 +8753,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>YSL圣罗兰银管02色</t>
+          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8772,7 +8776,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>倩碧有油润肤乳125ml</t>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8795,7 +8799,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+          <t>GUCCI 香水 茉莉100ML</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8818,7 +8822,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>SK2大红瓶清爽版80g</t>
+          <t>爱马仕李先生的花园淡香水100ml</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8841,7 +8845,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润版80g</t>
+          <t>爱马仕绯红火参古龙水100ml</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8864,7 +8868,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8887,7 +8891,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SK-II 小银瓶精华50ML</t>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8910,7 +8914,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>阿玛尼大师粉底液2号</t>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8933,7 +8937,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
+          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8956,7 +8960,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8979,7 +8983,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+          <t>MAC 无暇粉底液NC12 30ML</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -9002,7 +9006,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
+          <t>雅诗兰黛 红石榴面霜50ml</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -9025,7 +9029,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -9048,7 +9052,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>GUCCI 香水 茉莉100ML</t>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -9071,7 +9075,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>爱马仕李先生的花园淡香水100ml</t>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -9094,7 +9098,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>爱马仕绯红火参古龙水100ml</t>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -9117,7 +9121,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -9140,7 +9144,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -9163,7 +9167,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -9186,7 +9190,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -9209,7 +9213,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MAC妆前瞬间定妆喷雾100ML</t>
+          <t>兰芝马卡龙隔离30ml紫色</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -9232,7 +9236,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MAC 无暇粉底液NC12 30ML</t>
+          <t>兰芝马卡龙隔离30ml绿色</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -9255,7 +9259,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>雅诗兰黛 红石榴面霜50ml</t>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -9278,7 +9282,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>雅诗兰黛 红石榴洁面125ml</t>
+          <t>NARS蜜粉饼5894 效期24年</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -9301,7 +9305,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -9324,7 +9328,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -9347,7 +9351,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+          <t>古驰炼金师花园香草颂香水100ML</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -9370,7 +9374,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -9393,7 +9397,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -9416,7 +9420,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+          <t>YSL新款爱心唇釉610#</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -9439,7 +9443,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+          <t>宝格丽白茶淡香150ml</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -9462,7 +9466,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>兰芝马卡龙隔离30ml紫色</t>
+          <t>植村秀绿茶卸妆油150ml</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9485,7 +9489,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>兰芝马卡龙隔离30ml绿色</t>
+          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9508,7 +9512,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+          <t>NARS 水光绚色液体腮红 烟粉豆沙色 BEHAVE 7ml</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9531,7 +9535,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>NARS蜜粉饼5894 效期24年</t>
+          <t>Jo Malone祖玛珑英国梨与豌豆花香水30ml</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9554,7 +9558,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+          <t>兰蔻清爽防晒50ml*2新版</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9577,7 +9581,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SHISEIDO资生堂红腰子精华100ml</t>
+          <t>古驰炼金师花园狮之心香水100ML</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9600,7 +9604,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>古驰炼金师花园香草颂香水100ML</t>
+          <t>古驰炼金师花园桂之舞香水100ML</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9623,7 +9627,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>古驰炼金师花园沐光橙香水100ML</t>
+          <t>NARS液体腮红 INSATIABLE</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9646,7 +9650,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+          <t>NARS多功能腮红棒TRANCE 8G</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9669,7 +9673,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>YSL新款爱心唇釉610#</t>
+          <t>NARS多用腮红棒欲焰HOT TAKE 8G</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9684,7 +9688,11 @@
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -9692,7 +9700,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>宝格丽白茶淡香150ml</t>
+          <t>NARS多用腮红棒爱欲SEX APPEAL 8G</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9707,7 +9715,11 @@
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -9715,7 +9727,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>植村秀绿茶卸妆油150ml</t>
+          <t>NARS小粉金液体腮红WANDERLUST 7ML</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9738,7 +9750,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
+          <t>古驰竹韵浓香75ml</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9761,7 +9773,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>NARS 水光绚色液体腮红 烟粉豆沙色 BEHAVE 7ml</t>
+          <t>欧莱雅紫熨斗30ml 第三代</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9784,7 +9796,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Jo Malone祖玛珑英国梨与豌豆花香水30ml</t>
+          <t>迪奥新版浮雕睡莲洗面奶150ml</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9807,7 +9819,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>兰蔻清爽防晒50ml*2新版</t>
+          <t>Clarins娇韵诗焕颜紧致日霜50ml</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -9830,7 +9842,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>古驰炼金师花园狮之心香水100ML</t>
+          <t>YSL圣罗兰新版恒久无瑕粉底液LN1</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9853,7 +9865,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>古驰炼金师花园桂之舞香水100ML</t>
+          <t>兰蔻菁纯臻颜精萃水150ml</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9876,7 +9888,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>Hermes爱马仕大地淡香对装50ml*2</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9899,7 +9911,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>NARS多功能腮红棒TRANCE 8G</t>
+          <t>MAC魅可 反光镜唇蜜唇釉 228# 棕上镜 AESTHETIC 5ml</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9922,7 +9934,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>NARS多用腮红棒欲焰HOT TAKE 8G</t>
+          <t>伊丽莎白雅顿经典润泽护唇膏 SPF15 3.7g</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9937,11 +9949,7 @@
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -9949,7 +9957,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>NARS多用腮红棒爱欲SEX APPEAL 8G</t>
+          <t>资生堂第四代红腰子精华75ml</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9964,11 +9972,7 @@
       <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -9976,7 +9980,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>NARS小粉金液体腮红WANDERLUST 7ML</t>
+          <t>巴宝莉 粉红恋歌EDT 100ml</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9999,7 +10003,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>古驰竹韵浓香75ml</t>
+          <t>巴宝莉 情缘男士EDT100ml</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -10022,7 +10026,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>欧莱雅紫熨斗30ml 第三代</t>
+          <t>巴宝莉 我的巴宝莉黑色EDP 90ml</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -10045,7 +10049,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>迪奥新版浮雕睡莲洗面奶150ml</t>
+          <t>CK ONE 100ml(白盒)</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -10068,7 +10072,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Clarins娇韵诗焕颜紧致日霜50ml</t>
+          <t>CK ONE 200ml(白盒)</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -10091,7 +10095,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>YSL圣罗兰新版恒久无瑕粉底液LN1</t>
+          <t>CK BE 黑盒香水 100ml</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -10114,7 +10118,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>兰蔻菁纯臻颜精萃水150ml</t>
+          <t>CK BE 中性香水200ml黑盒</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -10137,7 +10141,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Hermes爱马仕大地淡香对装50ml*2</t>
+          <t>CK 喜欢你男士 50ml</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -10160,7 +10164,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>MAC魅可 反光镜唇蜜唇釉 228# 棕上镜 AESTHETIC 5ml</t>
+          <t>CK 喜欢你男士 100ml</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -10183,7 +10187,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿经典润泽护唇膏 SPF15 13g</t>
+          <t>CK 喜欢你女士100ml</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -10206,7 +10210,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>资生堂第四代红腰子精华75ml</t>
+          <t>CK 自由男士EDT100ml</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -10229,7 +10233,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>巴宝莉 粉红恋歌EDT 100ml</t>
+          <t>娇兰帝皇蜂姿蜜润修护精粹水 300mL</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -10252,7 +10256,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>巴宝莉 情缘男士EDT100ml</t>
+          <t>MAC 丝柔哑光唇膏 #669 WARM TEDDY 暖萌泰迪</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -10275,7 +10279,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>巴宝莉 我的巴宝莉黑色EDP 90ml</t>
+          <t>MAC 反光镜唇蜜唇釉 226# 当红镜 CASUAL 5ml</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -10298,12 +10302,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>CK ONE 100ml(白盒)</t>
+          <t>MAC魅可 轻尤雾弹 哑光唇釉973 5ml 新版</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -10321,12 +10325,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>CK ONE 200ml(白盒)</t>
+          <t>MAC魅可 聚光瓶粉底液 NW11 30ml</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -10344,12 +10348,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>CK BE 黑盒香水 100ml</t>
+          <t>MAC魅可 轻尤雾弹 哑光子弹头912 3.5ml</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -10367,12 +10371,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>CK BE 中性香水200ml黑盒</t>
+          <t>MAC魅可 聚光瓶粉底液 NC12 30ml</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -10390,12 +10394,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>CK 喜欢你男士 50ml</t>
+          <t>GUERLAIN娇兰双管精华50ml</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -10413,12 +10417,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>CK 喜欢你男士 100ml</t>
+          <t>NARS 水光绚色液体腮红 Secret Lover 7ml</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -10436,12 +10440,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>CK 喜欢你女士100ml</t>
+          <t>NARS细管哑光唇膏1.5G #136 GET LUCKY 丝绒瑰木</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -10459,12 +10463,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>CK 自由男士EDT100ml</t>
+          <t>资生堂 小针管眼霜（新款）20mL</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -10482,12 +10486,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>娇兰帝皇蜂姿蜜润修护精粹水 300mL</t>
+          <t>资生堂 蓝胖子防晒乳霜（新款）50mL</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -10505,12 +10509,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>MAC 丝柔哑光唇膏 #669 WARM TEDDY 暖萌泰迪</t>
+          <t>欧舒丹乳木果护手霜150ml</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -10528,12 +10532,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>MAC 反光镜唇蜜唇釉 226# 当红镜 CASUAL 5ml</t>
+          <t>资生堂盼丽风姿滋润面霜50ml新</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -10551,12 +10555,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MAC魅可 轻尤雾弹 哑光唇釉973 5ml 新版</t>
+          <t>资生堂红腰子面霜50ml新</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -10574,12 +10578,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MAC魅可 聚光瓶粉底液 NW11 30ml</t>
+          <t>Helena Rubinstein 赫莲娜 黑绷带活颜修护晚霜100ml（50%玻色因）</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -10591,259 +10595,6 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
     </row>
-    <row r="440">
-      <c r="A440" t="n">
-        <v>439</v>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>MAC魅可 轻尤雾弹 哑光子弹头912 3.5ml</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr"/>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
-      <c r="H440" t="inlineStr"/>
-      <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr"/>
-    </row>
-    <row r="441">
-      <c r="A441" t="n">
-        <v>440</v>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>MAC魅可 聚光瓶粉底液 NC12 30ml</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr"/>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="n">
-        <v>441</v>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>GUERLAIN娇兰双管精华50ml</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr"/>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
-    </row>
-    <row r="443">
-      <c r="A443" t="n">
-        <v>442</v>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>NARS 水光绚色液体腮红 Secret Lover 7ml</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr"/>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
-      <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
-      <c r="J443" t="inlineStr"/>
-      <c r="K443" t="inlineStr"/>
-    </row>
-    <row r="444">
-      <c r="A444" t="n">
-        <v>443</v>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>NARS细管哑光唇膏1.5G #136 GET LUCKY 丝绒瑰木</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr"/>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
-      <c r="K444" t="inlineStr"/>
-    </row>
-    <row r="445">
-      <c r="A445" t="n">
-        <v>444</v>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>资生堂 小针管眼霜（新款）20mL</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr"/>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
-      <c r="K445" t="inlineStr"/>
-    </row>
-    <row r="446">
-      <c r="A446" t="n">
-        <v>445</v>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>资生堂 蓝胖子防晒乳霜（新款）50mL</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr"/>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
-      <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr"/>
-      <c r="K446" t="inlineStr"/>
-    </row>
-    <row r="447">
-      <c r="A447" t="n">
-        <v>446</v>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>欧舒丹乳木果护手霜150ml</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr"/>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" t="n">
-        <v>447</v>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>资生堂盼丽风姿滋润面霜50ml新</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr"/>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
-      <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="n">
-        <v>448</v>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>资生堂红腰子面霜50ml新</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr"/>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="n">
-        <v>449</v>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Helena Rubinstein 赫莲娜 黑绷带活颜修护晚霜100ml（50%玻色因）</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr"/>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
